--- a/2026/COLOMBRES/ENERO/Enero COLOMBRES 360.xlsx
+++ b/2026/COLOMBRES/ENERO/Enero COLOMBRES 360.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\COLOMBRES\ENERO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\2026\COLOMBRES\ENERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A174764-7E23-4A78-8EF1-C58A79FD37C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2506757-7C40-4971-8463-C65C99731065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -18,14 +18,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$43</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$123</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$115</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="188">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -481,9 +481,6 @@
     <t>Claudia Guidobono</t>
   </si>
   <si>
-    <t>PABLO GARCIA</t>
-  </si>
-  <si>
     <t xml:space="preserve">
 Raquel Martinez</t>
   </si>
@@ -491,69 +488,15 @@
     <t>Diego Varas</t>
   </si>
   <si>
-    <t>Transf 19/12</t>
-  </si>
-  <si>
-    <t>Alterini Guido - Poda Ficus y Puesta a punto</t>
-  </si>
-  <si>
-    <t>Transf 05/12</t>
-  </si>
-  <si>
-    <t>Casa Ruan - Materiales electricos</t>
-  </si>
-  <si>
-    <t>Servisur - Instalacion de 4 artefactos iluminacion; tubos y listones + cableado</t>
-  </si>
-  <si>
-    <t>SAC - 2do SAC 2025</t>
-  </si>
-  <si>
-    <t>Debito 04/12</t>
-  </si>
-  <si>
     <t>HORARIOS DE ATENCION: 10 A 15HS - LUNES A VIERNES</t>
   </si>
   <si>
-    <t>Loschi Bruno - Limpieza de tanque de grupo electrogeno, provision de 30lts de gasoil y agregado de filtro</t>
-  </si>
-  <si>
-    <t>Transf 09/12</t>
-  </si>
-  <si>
-    <t>Debito 12/12</t>
-  </si>
-  <si>
-    <t>Debito 15/12</t>
-  </si>
-  <si>
-    <t>Compra de alfombra y alargue - Carrefour</t>
-  </si>
-  <si>
     <t>Servicio de fumigacion - Ortega Daniel - Mes de Octubre - Se adeudaba</t>
   </si>
   <si>
     <t>Ticket - Pago en efectivo</t>
   </si>
   <si>
-    <t>Transf 29/12</t>
-  </si>
-  <si>
-    <t>Roxana Goldemberg - Convenio deuda 2A</t>
-  </si>
-  <si>
-    <t>Ingreso adelanto plan de pagos 2A</t>
-  </si>
-  <si>
-    <t>Alterini Guido - Fumigacion</t>
-  </si>
-  <si>
-    <t>Transf 30/12</t>
-  </si>
-  <si>
-    <t>Gamboa Gustavo - Colocacion de pinches de seguridad con tarugos y tornillos en mediantera + Pintura en los mismos</t>
-  </si>
-  <si>
     <t>VTO 16/02</t>
   </si>
   <si>
@@ -563,9 +506,6 @@
     <t>Frank Matias Wallace - Mantenimiento ascensor ENERO</t>
   </si>
   <si>
-    <t>Alterini Guido - Mantenimiento de ENERO y compra de 4 agapanthus</t>
-  </si>
-  <si>
     <t>Articulos de limpieza -  Mes de ENERO</t>
   </si>
   <si>
@@ -593,23 +533,79 @@
     <t>Transf 09/1</t>
   </si>
   <si>
-    <t>Gamboa Gustavo - Trabajo realizado colocacion de pinches de seguridad con tarugos, tornillos en medianera. Se pintan los mismos.</t>
-  </si>
-  <si>
     <t>Transf 08/01</t>
+  </si>
+  <si>
+    <t>Leonardo Balcazza - Arreglo piso 13B  - Material y mano de obra</t>
+  </si>
+  <si>
+    <t>Debito 08/01</t>
+  </si>
+  <si>
+    <t>Loschi Bruno - Mantenimiento bimestral</t>
+  </si>
+  <si>
+    <t>Transf 15/01</t>
+  </si>
+  <si>
+    <t>Debito 13/01</t>
+  </si>
+  <si>
+    <t>Electricidad Alsina SA - Timer 24V - Arreglo extractor (terraza)</t>
+  </si>
+  <si>
+    <t>Transf 26/01</t>
+  </si>
+  <si>
+    <t>Transf 25/01</t>
+  </si>
+  <si>
+    <t>Cuello natalia (Destapacion) - Tramo interno 13B</t>
+  </si>
+  <si>
+    <t>Alterini Guido - Mantenimiento de ENERO - Maceton y tierra fertil 25dm</t>
+  </si>
+  <si>
+    <t>Transf 30/01</t>
+  </si>
+  <si>
+    <t>Debito 04/01</t>
+  </si>
+  <si>
+    <t>Mes de descanso</t>
+  </si>
+  <si>
+    <t>PABLO GARCIA - MATIAS EZEQUIEL GARCIA</t>
+  </si>
+  <si>
+    <t>Lireria - Sobres para entrega de expensas</t>
+  </si>
+  <si>
+    <t>Doartero Julio - Cambio de contactora</t>
+  </si>
+  <si>
+    <t>Materiales para el cambio de contactora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transf 30/01 </t>
+  </si>
+  <si>
+    <t>Deposito sin identificar del - 15/01</t>
+  </si>
+  <si>
+    <t>QUEDO PENDIENTE PARA FEBR3R0 PASAR UN EDESUR DE EN3RO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="25" x14ac:knownFonts="1">
     <font>
@@ -1231,7 +1227,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="195">
+  <cellXfs count="193">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1253,7 +1249,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="7" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1305,9 +1300,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="10" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1371,7 +1363,6 @@
     </xf>
     <xf numFmtId="44" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="19" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1392,32 +1383,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="24" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="20" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1450,13 +1421,81 @@
     <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="20" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1466,47 +1505,29 @@
     <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1520,9 +1541,6 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1532,9 +1550,6 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1550,21 +1565,6 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1919,113 +1919,113 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L127"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:L119"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="18.33203125" customWidth="1"/>
+    <col min="11" max="11" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="117" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="114" t="s">
         <v>122</v>
       </c>
-      <c r="B1" s="111"/>
+      <c r="B1" s="108"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="112" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="109" t="s">
         <v>123</v>
       </c>
-      <c r="B2" s="112"/>
-      <c r="C2" s="112"/>
-      <c r="D2" s="112"/>
-    </row>
-    <row r="3" spans="1:4" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="112" t="s">
-        <v>160</v>
-      </c>
-      <c r="B3" s="112"/>
-      <c r="C3" s="112"/>
-      <c r="D3" s="112"/>
-    </row>
-    <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="162" t="s">
+      <c r="B2" s="109"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="109"/>
+    </row>
+    <row r="3" spans="1:4" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="109" t="s">
+        <v>152</v>
+      </c>
+      <c r="B3" s="109"/>
+      <c r="C3" s="109"/>
+      <c r="D3" s="109"/>
+    </row>
+    <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="173" t="s">
         <v>124</v>
       </c>
-      <c r="B4" s="162"/>
-      <c r="C4" s="113"/>
-      <c r="D4" s="113"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="162"/>
-      <c r="B5" s="162"/>
-      <c r="C5" s="113"/>
-      <c r="D5" s="113"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="162"/>
-      <c r="B6" s="162"/>
-      <c r="C6" s="113"/>
-      <c r="D6" s="113"/>
-    </row>
-    <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="162"/>
-      <c r="B7" s="162"/>
-      <c r="C7" s="113"/>
-      <c r="D7" s="113"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B9" s="159" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B10" s="159"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B11" s="159"/>
-    </row>
-    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="163" t="s">
+      <c r="B4" s="173"/>
+      <c r="C4" s="110"/>
+      <c r="D4" s="110"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="173"/>
+      <c r="B5" s="173"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="173"/>
+      <c r="B6" s="173"/>
+      <c r="C6" s="110"/>
+      <c r="D6" s="110"/>
+    </row>
+    <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="173"/>
+      <c r="B7" s="173"/>
+      <c r="C7" s="110"/>
+      <c r="D7" s="110"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B9" s="172" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B10" s="172"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B11" s="172"/>
+    </row>
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="174" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="163"/>
-      <c r="C14" s="163"/>
-      <c r="D14" s="163"/>
-    </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="163"/>
-      <c r="B15" s="163"/>
-      <c r="C15" s="163"/>
-      <c r="D15" s="163"/>
-    </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="163"/>
-      <c r="B16" s="163"/>
-      <c r="C16" s="163"/>
-      <c r="D16" s="163"/>
-    </row>
-    <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="163"/>
-      <c r="B17" s="163"/>
-      <c r="C17" s="163"/>
-      <c r="D17" s="163"/>
-    </row>
-    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="174"/>
+      <c r="C14" s="174"/>
+      <c r="D14" s="174"/>
+    </row>
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="174"/>
+      <c r="B15" s="174"/>
+      <c r="C15" s="174"/>
+      <c r="D15" s="174"/>
+    </row>
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="174"/>
+      <c r="B16" s="174"/>
+      <c r="C16" s="174"/>
+      <c r="D16" s="174"/>
+    </row>
+    <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="174"/>
+      <c r="B17" s="174"/>
+      <c r="C17" s="174"/>
+      <c r="D17" s="174"/>
+    </row>
+    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>26</v>
       </c>
@@ -2033,955 +2033,895 @@
       <c r="C21" s="9"/>
       <c r="D21" s="13"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="27" t="s">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="B22" s="27"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-    </row>
-    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="26"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+    </row>
+    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>130</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="C23" s="149">
-        <v>1326237.8</v>
-      </c>
-      <c r="D23" s="82"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+        <v>160</v>
+      </c>
+      <c r="C23" s="138">
+        <v>1774070.07</v>
+      </c>
+      <c r="D23" s="80"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>84</v>
       </c>
       <c r="B24" s="5"/>
-      <c r="C24" s="149">
-        <f>-547901.99+259445.27</f>
-        <v>-288456.71999999997</v>
-      </c>
-      <c r="D24" s="82"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C24" s="138">
+        <f>-732912.7</f>
+        <v>-732912.7</v>
+      </c>
+      <c r="D24" s="80"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>83</v>
       </c>
       <c r="B25" s="5"/>
-      <c r="C25" s="149">
-        <v>0.19</v>
-      </c>
-      <c r="D25" s="82"/>
+      <c r="C25" s="138">
+        <v>0.63</v>
+      </c>
+      <c r="D25" s="80"/>
       <c r="G25" s="14"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="5" t="s">
-        <v>158</v>
-      </c>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="5"/>
       <c r="B26" s="5"/>
-      <c r="C26" s="149">
-        <f>511527+170508.96</f>
-        <v>682035.96</v>
-      </c>
-      <c r="D26" s="82"/>
+      <c r="C26" s="138"/>
+      <c r="D26" s="80"/>
       <c r="G26" s="14"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="48" t="s">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="47" t="s">
         <v>82</v>
       </c>
-      <c r="B27" s="48"/>
-      <c r="C27" s="108">
+      <c r="B27" s="47"/>
+      <c r="C27" s="106">
         <f>SUM(C23:C26)</f>
-        <v>1719817.23</v>
-      </c>
-      <c r="D27" s="83"/>
-      <c r="F27" s="157" t="s">
+        <v>1041158.0000000001</v>
+      </c>
+      <c r="D27" s="81"/>
+      <c r="F27" s="170" t="s">
         <v>145</v>
       </c>
-      <c r="G27" s="158"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G27" s="171"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>129</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="C28" s="149">
-        <v>1143884.73</v>
-      </c>
-      <c r="D28" s="116"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+        <v>160</v>
+      </c>
+      <c r="C28" s="138">
+        <v>1301013.8899999999</v>
+      </c>
+      <c r="D28" s="113"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>81</v>
       </c>
       <c r="B29" s="5"/>
-      <c r="C29" s="149">
-        <v>-248794.93</v>
-      </c>
-      <c r="D29" s="116"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C29" s="138">
+        <v>-282970.53000000003</v>
+      </c>
+      <c r="D29" s="113"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>83</v>
       </c>
       <c r="B30" s="5"/>
-      <c r="C30" s="149">
-        <v>0.2</v>
-      </c>
-      <c r="D30" s="116"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="5" t="s">
-        <v>158</v>
-      </c>
+      <c r="C30" s="138">
+        <v>0.64</v>
+      </c>
+      <c r="D30" s="113"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="5"/>
       <c r="B31" s="5"/>
-      <c r="C31" s="150">
-        <v>685850</v>
-      </c>
-      <c r="D31" s="116"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="48" t="s">
+      <c r="C31" s="139"/>
+      <c r="D31" s="113"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="47" t="s">
         <v>82</v>
       </c>
-      <c r="B32" s="115"/>
-      <c r="C32" s="49">
+      <c r="B32" s="112"/>
+      <c r="C32" s="48">
         <f>SUM(C28:C31)</f>
-        <v>1580940</v>
-      </c>
-      <c r="D32" s="83"/>
-    </row>
-    <row r="33" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>1018043.9999999999</v>
+      </c>
+      <c r="D32" s="81"/>
+    </row>
+    <row r="33" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="18" t="s">
         <v>0</v>
       </c>
       <c r="B33" s="18"/>
-      <c r="C33" s="20"/>
-      <c r="D33" s="84">
+      <c r="C33" s="19"/>
+      <c r="D33" s="82">
         <f>C27+C32</f>
-        <v>3300757.23</v>
+        <v>2059202</v>
       </c>
       <c r="E33" s="14"/>
       <c r="F33" s="14"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="27" t="s">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="B34" s="27"/>
-      <c r="C34" s="28"/>
-      <c r="D34" s="85"/>
+      <c r="B34" s="26"/>
+      <c r="C34" s="27"/>
+      <c r="D34" s="83"/>
       <c r="F34" s="14"/>
     </row>
-    <row r="35" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="57" t="s">
+    <row r="35" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="56" t="s">
         <v>39</v>
       </c>
       <c r="B35" s="5"/>
-      <c r="C35" s="193">
+      <c r="C35" s="138">
         <v>70000</v>
       </c>
-      <c r="D35" s="136" t="s">
-        <v>183</v>
+      <c r="D35" s="125" t="s">
+        <v>163</v>
       </c>
       <c r="G35" s="14"/>
     </row>
-    <row r="36" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="118" t="s">
+    <row r="36" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="115" t="s">
         <v>131</v>
       </c>
-      <c r="B36" s="110" t="s">
-        <v>175</v>
-      </c>
-      <c r="C36" s="149">
+      <c r="B36" s="107" t="s">
+        <v>156</v>
+      </c>
+      <c r="C36" s="138">
         <v>211800</v>
       </c>
-      <c r="D36" s="136" t="s">
-        <v>168</v>
+      <c r="D36" s="125" t="s">
+        <v>178</v>
       </c>
       <c r="G36" s="14"/>
     </row>
-    <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="18" t="s">
         <v>34</v>
       </c>
       <c r="B37" s="18"/>
-      <c r="C37" s="31"/>
-      <c r="D37" s="84">
+      <c r="C37" s="30"/>
+      <c r="D37" s="82">
         <f>SUM(C35:C36)</f>
         <v>281800</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="25" t="s">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="B38" s="26"/>
-      <c r="C38" s="29"/>
-      <c r="D38" s="59"/>
-    </row>
-    <row r="39" spans="1:7" s="34" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="160" t="s">
+      <c r="B38" s="25"/>
+      <c r="C38" s="28"/>
+      <c r="D38" s="57"/>
+    </row>
+    <row r="39" spans="1:7" s="33" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="166" t="s">
         <v>127</v>
       </c>
-      <c r="B39" s="161"/>
-      <c r="C39" s="151">
-        <v>175054.97</v>
-      </c>
-      <c r="D39" s="135" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="160" t="s">
+      <c r="B39" s="167"/>
+      <c r="C39" s="140" t="s">
+        <v>180</v>
+      </c>
+      <c r="D39" s="124"/>
+    </row>
+    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="166" t="s">
         <v>128</v>
       </c>
-      <c r="B40" s="161"/>
-      <c r="C40" s="152">
+      <c r="B40" s="167"/>
+      <c r="C40" s="147">
         <v>4203</v>
       </c>
-      <c r="D40" s="135" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="18" t="s">
+      <c r="D40" s="124" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B41" s="18"/>
-      <c r="C41" s="31"/>
-      <c r="D41" s="86">
+      <c r="B41" s="25"/>
+      <c r="C41" s="30"/>
+      <c r="D41" s="84">
         <f>SUM(C39:C40)</f>
-        <v>179257.97</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" s="27" t="s">
+        <v>4203</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="B42" s="19"/>
-      <c r="C42" s="32"/>
-      <c r="D42" s="87"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="5" t="s">
+      <c r="B42" s="148"/>
+      <c r="C42" s="31"/>
+      <c r="D42" s="85"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="80" t="s">
         <v>132</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="C43" s="194">
+      <c r="B43" s="80" t="s">
+        <v>160</v>
+      </c>
+      <c r="C43" s="141">
         <v>2082831.51</v>
       </c>
-      <c r="D43" s="135" t="s">
-        <v>159</v>
-      </c>
-      <c r="F43" s="119"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="5" t="s">
+      <c r="D43" s="124" t="s">
+        <v>169</v>
+      </c>
+      <c r="F43" s="116"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="80" t="s">
         <v>133</v>
       </c>
-      <c r="B44" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="C44" s="192">
+      <c r="B44" s="80" t="s">
+        <v>160</v>
+      </c>
+      <c r="C44" s="149">
         <v>24115.91</v>
       </c>
-      <c r="D44" s="135" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="5" t="s">
+      <c r="D44" s="124" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="80" t="s">
         <v>134</v>
       </c>
-      <c r="B45" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="C45" s="192">
+      <c r="B45" s="80" t="s">
+        <v>160</v>
+      </c>
+      <c r="C45" s="149">
         <v>217043.12</v>
       </c>
-      <c r="D45" s="135" t="str">
+      <c r="D45" s="124" t="str">
         <f>D44</f>
-        <v>Debito 12/12</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="5" t="s">
+        <v>Debito 13/01</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="80" t="s">
         <v>135</v>
       </c>
-      <c r="B46" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="C46" s="192">
+      <c r="B46" s="80" t="s">
+        <v>160</v>
+      </c>
+      <c r="C46" s="149">
         <v>397626.72</v>
       </c>
-      <c r="D46" s="133" t="str">
+      <c r="D46" s="122" t="str">
         <f>D45</f>
-        <v>Debito 12/12</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="18" t="s">
+        <v>Debito 13/01</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="B47" s="19"/>
-      <c r="C47" s="33"/>
-      <c r="D47" s="86">
+      <c r="B47" s="148"/>
+      <c r="C47" s="32"/>
+      <c r="D47" s="84">
         <f>SUM(C43:C46)</f>
         <v>2721617.26</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" s="27" t="s">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="B48" s="19"/>
-      <c r="C48" s="32"/>
-      <c r="D48" s="87"/>
-    </row>
-    <row r="49" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+      <c r="B48" s="148"/>
+      <c r="C48" s="31"/>
+      <c r="D48" s="85"/>
+    </row>
+    <row r="49" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="95" t="s">
         <v>136</v>
       </c>
-      <c r="B49" s="5"/>
-      <c r="C49" s="192">
+      <c r="B49" s="80"/>
+      <c r="C49" s="149">
         <v>569002.89</v>
       </c>
-      <c r="D49" s="132" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="5" t="s">
+      <c r="D49" s="121" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="80" t="s">
         <v>125</v>
       </c>
-      <c r="B50" s="5"/>
-      <c r="C50" s="192">
+      <c r="B50" s="80"/>
+      <c r="C50" s="149">
         <v>20769.7</v>
       </c>
-      <c r="D50" s="132" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="5" t="s">
+      <c r="D50" s="121" t="s">
+        <v>167</v>
+      </c>
+      <c r="F50" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="80" t="s">
         <v>138</v>
       </c>
-      <c r="B51" s="5"/>
-      <c r="C51" s="192">
+      <c r="B51" s="80"/>
+      <c r="C51" s="149">
         <v>864000.26</v>
       </c>
-      <c r="D51" s="132" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="169" t="s">
+      <c r="D51" s="121" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="168" t="s">
+        <v>157</v>
+      </c>
+      <c r="B52" s="169"/>
+      <c r="C52" s="149">
+        <v>204149</v>
+      </c>
+      <c r="D52" s="121" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="164" t="s">
+        <v>170</v>
+      </c>
+      <c r="B53" s="165"/>
+      <c r="C53" s="149">
+        <v>100000</v>
+      </c>
+      <c r="D53" s="123" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="166" t="s">
+        <v>153</v>
+      </c>
+      <c r="B54" s="167"/>
+      <c r="C54" s="149">
+        <v>35200</v>
+      </c>
+      <c r="D54" s="123" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="B55" s="25"/>
+      <c r="C55" s="30"/>
+      <c r="D55" s="84">
+        <f>SUM(C49:C54)</f>
+        <v>1793121.85</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="B56" s="25"/>
+      <c r="C56" s="30"/>
+      <c r="D56" s="87"/>
+    </row>
+    <row r="57" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="150" t="s">
+        <v>164</v>
+      </c>
+      <c r="B57" s="151"/>
+      <c r="C57" s="149">
+        <v>11850</v>
+      </c>
+      <c r="D57" s="118" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="150" t="s">
+        <v>182</v>
+      </c>
+      <c r="B58" s="151"/>
+      <c r="C58" s="149">
+        <v>5400</v>
+      </c>
+      <c r="D58" s="118" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="152" t="s">
+        <v>165</v>
+      </c>
+      <c r="B59" s="153"/>
+      <c r="C59" s="149">
+        <v>184942.62</v>
+      </c>
+      <c r="D59" s="118" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="166" t="s">
+        <v>177</v>
+      </c>
+      <c r="B60" s="167"/>
+      <c r="C60" s="149">
+        <v>250000</v>
+      </c>
+      <c r="D60" s="118" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="152" t="s">
+        <v>173</v>
+      </c>
+      <c r="B61" s="151"/>
+      <c r="C61" s="149">
+        <v>96111.67</v>
+      </c>
+      <c r="D61" s="118" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="166" t="s">
+        <v>168</v>
+      </c>
+      <c r="B62" s="167"/>
+      <c r="C62" s="149">
+        <v>750000</v>
+      </c>
+      <c r="D62" s="121" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="145" t="s">
+        <v>184</v>
+      </c>
+      <c r="B63" s="146"/>
+      <c r="C63" s="149">
+        <v>128083.59</v>
+      </c>
+      <c r="D63" s="144" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="166" t="s">
+        <v>183</v>
+      </c>
+      <c r="B64" s="167"/>
+      <c r="C64" s="149">
+        <v>180000</v>
+      </c>
+      <c r="D64" s="144" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="166" t="s">
+        <v>161</v>
+      </c>
+      <c r="B65" s="167"/>
+      <c r="C65" s="149">
+        <v>35000</v>
+      </c>
+      <c r="D65" s="123" t="s">
+        <v>162</v>
+      </c>
+      <c r="E65" s="39"/>
+      <c r="F65" s="39"/>
+    </row>
+    <row r="66" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="164" t="s">
+        <v>158</v>
+      </c>
+      <c r="B66" s="165"/>
+      <c r="C66" s="141">
+        <v>0</v>
+      </c>
+      <c r="D66" s="123"/>
+    </row>
+    <row r="67" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B67" s="24"/>
+      <c r="C67" s="24"/>
+      <c r="D67" s="90">
+        <f>SUM(C57:C66)</f>
+        <v>1641387.8800000001</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B68" s="154"/>
+      <c r="C68" s="19"/>
+      <c r="D68" s="87"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="80" t="s">
+        <v>137</v>
+      </c>
+      <c r="B69" s="80"/>
+      <c r="C69" s="149">
+        <v>65343</v>
+      </c>
+      <c r="D69" s="91"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="80" t="s">
+        <v>126</v>
+      </c>
+      <c r="B70" s="80"/>
+      <c r="C70" s="149">
+        <f>1270.8+130081.56+168.5+1080+1392+150+600+950+1062</f>
+        <v>136754.85999999999</v>
+      </c>
+      <c r="D70" s="89"/>
+    </row>
+    <row r="71" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="B71" s="44"/>
+      <c r="C71" s="92"/>
+      <c r="D71" s="84">
+        <f>SUM(C69:C70)</f>
+        <v>202097.86</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="5"/>
+      <c r="B72" s="5"/>
+      <c r="C72" s="80"/>
+      <c r="D72" s="93"/>
+    </row>
+    <row r="73" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="161" t="s">
+        <v>144</v>
+      </c>
+      <c r="B73" s="162"/>
+      <c r="C73" s="163"/>
+      <c r="D73" s="94">
+        <f>10000000-8703429.85</f>
+        <v>1296570.1500000004</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="1"/>
+      <c r="C74" s="95"/>
+      <c r="D74" s="96"/>
+      <c r="E74" s="39"/>
+    </row>
+    <row r="75" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B75" s="10"/>
+      <c r="C75" s="97"/>
+      <c r="D75" s="98">
+        <f>(SUM(D28:D73))</f>
+        <v>10000000</v>
+      </c>
+      <c r="E75" s="39"/>
+      <c r="F75" s="39"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C76" s="95"/>
+      <c r="D76" s="95"/>
+      <c r="F76" s="117"/>
+    </row>
+    <row r="77" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C77" s="95"/>
+      <c r="D77" s="95"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B78" s="12"/>
+      <c r="C78" s="99"/>
+      <c r="D78" s="100"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="159"/>
+      <c r="B79" s="160"/>
+      <c r="C79" s="88"/>
+      <c r="D79" s="86"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="159"/>
+      <c r="B80" s="160"/>
+      <c r="C80" s="88"/>
+      <c r="D80" s="86"/>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="103"/>
+      <c r="B81" s="104"/>
+      <c r="C81" s="88"/>
+      <c r="D81" s="86"/>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" s="42"/>
+      <c r="B82" s="41"/>
+      <c r="C82" s="49"/>
+      <c r="D82" s="49">
+        <f>SUM(C79:C81)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="B85" s="20"/>
+      <c r="C85" s="21"/>
+      <c r="D85" s="126">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="87" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B87" s="10"/>
+      <c r="C87" s="4"/>
+      <c r="D87" s="58">
+        <f>D82+D85</f>
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="89" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="78" t="s">
+        <v>31</v>
+      </c>
+      <c r="B89" s="79">
+        <f>D75</f>
+        <v>10000000</v>
+      </c>
+      <c r="C89" s="39"/>
+    </row>
+    <row r="90" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="78" t="s">
+        <v>32</v>
+      </c>
+      <c r="B90" s="79">
+        <f>D75-D73</f>
+        <v>8703429.8499999996</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="78" t="s">
+        <v>43</v>
+      </c>
+      <c r="B91" s="79">
+        <f>D87-D85</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="78" t="s">
+        <v>88</v>
+      </c>
+      <c r="B92" s="79">
+        <f>D87</f>
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" s="158" t="s">
+        <v>159</v>
+      </c>
+      <c r="B95" s="158"/>
+      <c r="C95" s="158"/>
+      <c r="D95" s="158"/>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" s="158"/>
+      <c r="B96" s="158"/>
+      <c r="C96" s="158"/>
+      <c r="D96" s="158"/>
+    </row>
+    <row r="97" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="158"/>
+      <c r="B97" s="158"/>
+      <c r="C97" s="158"/>
+      <c r="D97" s="158"/>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="B99" s="35"/>
+    </row>
+    <row r="100" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="B100" s="105">
+        <v>5322816.5199999996</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="B101" s="36">
+        <f>PRORRATEO!H34</f>
+        <v>9786183.0700000003</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="B102" s="89">
+        <f>B114</f>
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="B103" s="120"/>
+    </row>
+    <row r="104" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="B52" s="170"/>
-      <c r="C52" s="154">
-        <v>177521</v>
-      </c>
-      <c r="D52" s="132" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="167" t="s">
-        <v>161</v>
-      </c>
-      <c r="B53" s="168"/>
-      <c r="C53" s="154">
-        <v>220000</v>
-      </c>
-      <c r="D53" s="134" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="B54" s="109"/>
-      <c r="C54" s="154">
-        <v>30600</v>
-      </c>
-      <c r="D54" s="134" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="B55" s="18"/>
-      <c r="C55" s="31"/>
-      <c r="D55" s="86">
-        <f>SUM(C49:C54)</f>
-        <v>1881893.85</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="B56" s="18"/>
-      <c r="C56" s="31"/>
-      <c r="D56" s="89"/>
-    </row>
-    <row r="57" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="122" t="s">
-        <v>165</v>
-      </c>
-      <c r="B57" s="123"/>
-      <c r="C57" s="154">
-        <v>71000</v>
-      </c>
-      <c r="D57" s="124" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="122" t="s">
-        <v>184</v>
-      </c>
-      <c r="B58" s="123"/>
-      <c r="C58" s="192">
-        <v>11850</v>
-      </c>
-      <c r="D58" s="124" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="122" t="s">
-        <v>185</v>
-      </c>
-      <c r="B59" s="123"/>
-      <c r="C59" s="192">
-        <v>184942.62</v>
-      </c>
-      <c r="D59" s="124" t="s">
+      <c r="B104" s="120">
+        <v>-31400</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="B105" s="120">
+        <f>-B90</f>
+        <v>-8703429.8499999996</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B106" s="89">
+        <f>-(B91)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B107" s="105">
+        <f>SUM(B100:B106)</f>
+        <v>6874169.7400000002</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B108" s="37"/>
+      <c r="C108" s="39"/>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" s="157" t="s">
+        <v>78</v>
+      </c>
+      <c r="B110" s="157"/>
+    </row>
+    <row r="111" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="157"/>
+      <c r="B111" s="157"/>
+    </row>
+    <row r="112" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="101" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="160" t="s">
-        <v>177</v>
-      </c>
-      <c r="B60" s="161"/>
-      <c r="C60" s="154">
-        <v>130000</v>
-      </c>
-      <c r="D60" s="124" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="122" t="s">
-        <v>171</v>
-      </c>
-      <c r="B61" s="123"/>
-      <c r="C61" s="154">
-        <v>35200</v>
-      </c>
-      <c r="D61" s="124" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="160" t="s">
-        <v>187</v>
-      </c>
-      <c r="B62" s="161"/>
-      <c r="C62" s="192">
-        <v>250000</v>
-      </c>
-      <c r="D62" s="132" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="129" t="s">
-        <v>154</v>
-      </c>
-      <c r="B63" s="130"/>
-      <c r="C63" s="154">
-        <v>250000</v>
-      </c>
-      <c r="D63" s="132" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="167" t="s">
-        <v>157</v>
-      </c>
-      <c r="B64" s="168"/>
-      <c r="C64" s="154">
-        <v>100000</v>
-      </c>
-      <c r="D64" s="132" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="105" t="s">
-        <v>156</v>
-      </c>
-      <c r="B65" s="131"/>
-      <c r="C65" s="154">
-        <v>20100</v>
-      </c>
-      <c r="D65" s="132" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="105" t="s">
-        <v>156</v>
-      </c>
-      <c r="B66" s="131"/>
-      <c r="C66" s="154">
-        <v>120100</v>
-      </c>
-      <c r="D66" s="134" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="160" t="s">
-        <v>181</v>
-      </c>
-      <c r="B67" s="161"/>
-      <c r="C67" s="192">
-        <v>35000</v>
-      </c>
-      <c r="D67" s="134" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="160" t="s">
-        <v>173</v>
-      </c>
-      <c r="B68" s="161"/>
-      <c r="C68" s="154">
-        <v>250000</v>
-      </c>
-      <c r="D68" s="134" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="167" t="s">
-        <v>178</v>
-      </c>
-      <c r="B69" s="168"/>
-      <c r="C69" s="153">
-        <v>196600</v>
-      </c>
-      <c r="D69" s="134" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="18" t="s">
+      <c r="B112" s="29">
+        <v>240000</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="101" t="s">
+        <v>186</v>
+      </c>
+      <c r="B113" s="29">
+        <v>260000</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A114" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="B70" s="27"/>
-      <c r="C70" s="25"/>
-      <c r="D70" s="92">
-        <f>SUM(C57:C69)</f>
-        <v>1654792.62</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="B71" s="58"/>
-      <c r="C71" s="20"/>
-      <c r="D71" s="89"/>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="B72" s="5"/>
-      <c r="C72" s="154">
-        <v>65343</v>
-      </c>
-      <c r="D72" s="93"/>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="B73" s="5"/>
-      <c r="C73" s="154">
-        <f>131081.78+120.75+990+780+211.2+1450.8</f>
-        <v>134634.53</v>
-      </c>
-      <c r="D73" s="91"/>
-    </row>
-    <row r="74" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="45" t="s">
-        <v>34</v>
-      </c>
-      <c r="B74" s="45"/>
-      <c r="C74" s="94"/>
-      <c r="D74" s="86">
-        <f>SUM(C72:C73)</f>
-        <v>199977.53</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="5"/>
-      <c r="B75" s="5"/>
-      <c r="C75" s="82"/>
-      <c r="D75" s="95"/>
-    </row>
-    <row r="76" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="164" t="s">
-        <v>144</v>
-      </c>
-      <c r="B76" s="165"/>
-      <c r="C76" s="166"/>
-      <c r="D76" s="96">
-        <f>10000000-8953305.51-250000</f>
-        <v>796694.49000000022</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="1"/>
-      <c r="C77" s="97"/>
-      <c r="D77" s="98"/>
-      <c r="E77" s="40"/>
-    </row>
-    <row r="78" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B78" s="10"/>
-      <c r="C78" s="99"/>
-      <c r="D78" s="100">
-        <f>(SUM(D28:D76))</f>
-        <v>11016790.949999999</v>
-      </c>
-      <c r="E78" s="40"/>
-      <c r="F78" s="40"/>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C79" s="97"/>
-      <c r="D79" s="97"/>
-      <c r="F79" s="121"/>
-    </row>
-    <row r="80" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C80" s="97"/>
-      <c r="D80" s="97"/>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A81" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B81" s="12"/>
-      <c r="C81" s="101"/>
-      <c r="D81" s="102"/>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A82" s="160"/>
-      <c r="B82" s="161"/>
-      <c r="C82" s="90"/>
-      <c r="D82" s="88"/>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A83" s="160"/>
-      <c r="B83" s="161"/>
-      <c r="C83" s="90"/>
-      <c r="D83" s="88"/>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A84" s="105"/>
-      <c r="B84" s="106"/>
-      <c r="C84" s="90"/>
-      <c r="D84" s="88"/>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A85" s="43"/>
-      <c r="B85" s="42"/>
-      <c r="C85" s="50"/>
-      <c r="D85" s="50">
-        <f>SUM(C82:C84)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="87" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A88" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="B88" s="21"/>
-      <c r="C88" s="22"/>
-      <c r="D88" s="137">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="90" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B90" s="10"/>
-      <c r="C90" s="4"/>
-      <c r="D90" s="60">
-        <f>D85+D88</f>
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="92" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="80" t="s">
-        <v>31</v>
-      </c>
-      <c r="B92" s="81">
-        <f>D78</f>
-        <v>11016790.949999999</v>
-      </c>
-      <c r="C92" s="40"/>
-    </row>
-    <row r="93" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="80" t="s">
-        <v>32</v>
-      </c>
-      <c r="B93" s="81">
-        <f>D78-D76</f>
-        <v>10220096.459999999</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="80" t="s">
-        <v>43</v>
-      </c>
-      <c r="B94" s="81">
-        <f>D90-D88</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="80" t="s">
-        <v>88</v>
-      </c>
-      <c r="B95" s="81">
-        <f>D90</f>
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="B98" s="173"/>
-      <c r="C98" s="173"/>
-      <c r="D98" s="173"/>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A99" s="173"/>
-      <c r="B99" s="173"/>
-      <c r="C99" s="173"/>
-      <c r="D99" s="173"/>
-    </row>
-    <row r="100" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="173"/>
-      <c r="B100" s="173"/>
-      <c r="C100" s="173"/>
-      <c r="D100" s="173"/>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A102" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="B102" s="36"/>
-    </row>
-    <row r="103" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="B103" s="107">
-        <v>4320478.1799999978</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="B104" s="37">
-        <f>PRORRATEO!H34</f>
-        <v>10025643.850000001</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="B105" s="91">
-        <f>B122</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="17" t="s">
-        <v>143</v>
-      </c>
-      <c r="B106" s="126"/>
-    </row>
-    <row r="107" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="17" t="s">
-        <v>170</v>
-      </c>
-      <c r="B107" s="91">
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="B108" s="126">
-        <v>-120000</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A109" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="B109" s="126">
-        <f>-B93</f>
-        <v>-10220096.459999999</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A110" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="B110" s="91">
-        <f>-(B94)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A111" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="B111" s="107">
-        <f>SUM(B103:B110)</f>
-        <v>4306025.57</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B112" s="38"/>
-      <c r="C112" s="40"/>
-    </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A114" s="172" t="s">
-        <v>78</v>
-      </c>
-      <c r="B114" s="172"/>
-    </row>
-    <row r="115" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="172"/>
-      <c r="B115" s="172"/>
-    </row>
-    <row r="116" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="103"/>
-      <c r="B116" s="30"/>
-    </row>
-    <row r="117" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="103"/>
-      <c r="B117" s="30"/>
-    </row>
-    <row r="118" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="103"/>
-      <c r="B118" s="30"/>
-    </row>
-    <row r="119" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="103"/>
-      <c r="B119" s="30"/>
-    </row>
-    <row r="120" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="103"/>
-      <c r="B120" s="30"/>
-    </row>
-    <row r="121" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="103"/>
-      <c r="B121" s="120"/>
-    </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A122" s="41" t="s">
-        <v>11</v>
-      </c>
-      <c r="B122" s="104">
-        <f>SUM(B116:B121)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="L123" s="8"/>
-    </row>
-    <row r="124" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="171"/>
-      <c r="B124" s="171"/>
-      <c r="C124" s="171"/>
-      <c r="D124" s="171"/>
-    </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A125" s="171"/>
-      <c r="B125" s="171"/>
-      <c r="C125" s="171"/>
-      <c r="D125" s="171"/>
-    </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A126" s="171"/>
-      <c r="B126" s="171"/>
-      <c r="C126" s="171"/>
-      <c r="D126" s="171"/>
-    </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A127" s="171"/>
-      <c r="B127" s="171"/>
-      <c r="C127" s="171"/>
-      <c r="D127" s="171"/>
+      <c r="B114" s="102">
+        <f>SUM(B112:B113)</f>
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L115" s="8"/>
+    </row>
+    <row r="116" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="156"/>
+      <c r="B116" s="156"/>
+      <c r="C116" s="156"/>
+      <c r="D116" s="156"/>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A117" s="156"/>
+      <c r="B117" s="156"/>
+      <c r="C117" s="156"/>
+      <c r="D117" s="156"/>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A118" s="156"/>
+      <c r="B118" s="156"/>
+      <c r="C118" s="156"/>
+      <c r="D118" s="156"/>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A119" s="156"/>
+      <c r="B119" s="156"/>
+      <c r="C119" s="156"/>
+      <c r="D119" s="156"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A124:D127"/>
-    <mergeCell ref="A114:B115"/>
-    <mergeCell ref="A98:D100"/>
-    <mergeCell ref="A83:B83"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="A76:C76"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A67:B67"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A68:B68"/>
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="A39:B39"/>
     <mergeCell ref="A4:B7"/>
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="A14:D17"/>
+    <mergeCell ref="A73:C73"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A116:D119"/>
+    <mergeCell ref="A110:B111"/>
+    <mergeCell ref="A95:D97"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="A79:B79"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2992,677 +2932,675 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:S42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5546875" customWidth="1"/>
-    <col min="3" max="3" width="4.33203125" customWidth="1"/>
-    <col min="4" max="4" width="18.5546875" customWidth="1"/>
-    <col min="5" max="5" width="0.109375" customWidth="1"/>
-    <col min="6" max="6" width="5.109375" customWidth="1"/>
-    <col min="7" max="7" width="14.109375" customWidth="1"/>
+    <col min="2" max="2" width="5.5703125" customWidth="1"/>
+    <col min="3" max="3" width="4.28515625" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="5.140625" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="7.6640625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5546875" customWidth="1"/>
-    <col min="11" max="11" width="11.109375" customWidth="1"/>
-    <col min="12" max="12" width="14.44140625" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" customWidth="1"/>
-    <col min="14" max="14" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.33203125" customWidth="1"/>
-    <col min="16" max="16" width="14.109375" customWidth="1"/>
-    <col min="17" max="17" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.7109375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" customWidth="1"/>
+    <col min="14" max="14" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.28515625" customWidth="1"/>
+    <col min="16" max="16" width="14.140625" customWidth="1"/>
+    <col min="17" max="17" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
-      <c r="B1" s="174" t="s">
+      <c r="B1" s="181" t="s">
         <v>147</v>
       </c>
-      <c r="C1" s="174"/>
-      <c r="D1" s="174"/>
-      <c r="E1" s="174"/>
-      <c r="F1" s="174"/>
-      <c r="G1" s="174"/>
-      <c r="H1" s="174"/>
-      <c r="I1" s="174"/>
-      <c r="J1" s="174"/>
-      <c r="K1" s="174"/>
+      <c r="C1" s="181"/>
+      <c r="D1" s="181"/>
+      <c r="E1" s="181"/>
+      <c r="F1" s="181"/>
+      <c r="G1" s="181"/>
+      <c r="H1" s="181"/>
+      <c r="I1" s="181"/>
+      <c r="J1" s="181"/>
+      <c r="K1" s="181"/>
       <c r="L1" s="6"/>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
       <c r="O1" s="6"/>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
-      <c r="B2" s="174"/>
-      <c r="C2" s="174"/>
-      <c r="D2" s="174"/>
-      <c r="E2" s="174"/>
-      <c r="F2" s="174"/>
-      <c r="G2" s="174"/>
-      <c r="H2" s="174"/>
-      <c r="I2" s="174"/>
-      <c r="J2" s="174"/>
-      <c r="K2" s="174"/>
+      <c r="B2" s="181"/>
+      <c r="C2" s="181"/>
+      <c r="D2" s="181"/>
+      <c r="E2" s="181"/>
+      <c r="F2" s="181"/>
+      <c r="G2" s="181"/>
+      <c r="H2" s="181"/>
+      <c r="I2" s="181"/>
+      <c r="J2" s="181"/>
+      <c r="K2" s="181"/>
       <c r="L2" s="7" t="s">
         <v>4</v>
       </c>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
-      <c r="O2" s="155">
+      <c r="O2" s="142">
         <v>10000000</v>
       </c>
-      <c r="P2" s="47"/>
+      <c r="P2" s="46"/>
       <c r="Q2" s="14"/>
     </row>
-    <row r="3" spans="1:19" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
-      <c r="B3" s="175"/>
-      <c r="C3" s="175"/>
-      <c r="D3" s="175"/>
-      <c r="E3" s="175"/>
-      <c r="F3" s="175"/>
-      <c r="G3" s="175"/>
-      <c r="H3" s="175"/>
-      <c r="I3" s="175"/>
-      <c r="J3" s="175"/>
-      <c r="K3" s="175"/>
+      <c r="B3" s="182"/>
+      <c r="C3" s="182"/>
+      <c r="D3" s="182"/>
+      <c r="E3" s="182"/>
+      <c r="F3" s="182"/>
+      <c r="G3" s="182"/>
+      <c r="H3" s="182"/>
+      <c r="I3" s="182"/>
+      <c r="J3" s="182"/>
+      <c r="K3" s="182"/>
       <c r="L3" s="7" t="s">
         <v>93</v>
       </c>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
-      <c r="O3" s="156">
+      <c r="O3" s="143">
         <v>1000000</v>
       </c>
-      <c r="P3" s="51"/>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A4" s="188" t="s">
+      <c r="P3" s="50"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="175" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="190" t="s">
+      <c r="B4" s="177" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="178" t="s">
+      <c r="C4" s="179" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="178" t="s">
+      <c r="D4" s="179" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="178" t="s">
+      <c r="E4" s="179" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="178" t="s">
+      <c r="F4" s="179" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="178" t="s">
+      <c r="G4" s="179" t="s">
         <v>89</v>
       </c>
-      <c r="H4" s="178" t="s">
+      <c r="H4" s="179" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="178" t="s">
+      <c r="I4" s="179" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="183" t="s">
+      <c r="J4" s="188" t="s">
         <v>50</v>
       </c>
-      <c r="K4" s="180" t="s">
+      <c r="K4" s="186" t="s">
         <v>47</v>
       </c>
-      <c r="L4" s="180" t="s">
+      <c r="L4" s="186" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="180" t="s">
+      <c r="M4" s="186" t="s">
         <v>46</v>
       </c>
-      <c r="N4" s="186" t="s">
+      <c r="N4" s="191" t="s">
         <v>87</v>
       </c>
-      <c r="O4" s="54" t="s">
+      <c r="O4" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="P4" s="176" t="s">
+      <c r="P4" s="183" t="s">
         <v>85</v>
       </c>
-      <c r="S4" s="40"/>
-    </row>
-    <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="189"/>
-      <c r="B5" s="191"/>
-      <c r="C5" s="182"/>
-      <c r="D5" s="182"/>
-      <c r="E5" s="179"/>
-      <c r="F5" s="182"/>
-      <c r="G5" s="182"/>
-      <c r="H5" s="182"/>
-      <c r="I5" s="179"/>
-      <c r="J5" s="184"/>
-      <c r="K5" s="181"/>
-      <c r="L5" s="185"/>
-      <c r="M5" s="181"/>
-      <c r="N5" s="187"/>
-      <c r="O5" s="52" t="str">
+      <c r="S4" s="39"/>
+    </row>
+    <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="176"/>
+      <c r="B5" s="178"/>
+      <c r="C5" s="180"/>
+      <c r="D5" s="180"/>
+      <c r="E5" s="185"/>
+      <c r="F5" s="180"/>
+      <c r="G5" s="180"/>
+      <c r="H5" s="180"/>
+      <c r="I5" s="185"/>
+      <c r="J5" s="189"/>
+      <c r="K5" s="187"/>
+      <c r="L5" s="190"/>
+      <c r="M5" s="187"/>
+      <c r="N5" s="192"/>
+      <c r="O5" s="51" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 16/02</v>
       </c>
-      <c r="P5" s="177"/>
-    </row>
-    <row r="6" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P5" s="184"/>
+    </row>
+    <row r="6" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="55">
+      <c r="B6" s="54">
         <v>1</v>
       </c>
-      <c r="C6" s="55" t="s">
+      <c r="C6" s="54" t="s">
         <v>51</v>
       </c>
-      <c r="D6" s="55" t="s">
+      <c r="D6" s="54" t="s">
         <v>95</v>
       </c>
-      <c r="E6" s="55"/>
-      <c r="F6" s="61">
+      <c r="E6" s="54"/>
+      <c r="F6" s="59">
         <v>4.57</v>
       </c>
-      <c r="G6" s="62">
-        <v>457000.01</v>
-      </c>
-      <c r="H6" s="63">
+      <c r="G6" s="60">
+        <v>507700.01</v>
+      </c>
+      <c r="H6" s="61">
         <f>G6</f>
-        <v>457000.01</v>
-      </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="65">
+        <v>507700.01</v>
+      </c>
+      <c r="I6" s="62"/>
+      <c r="J6" s="63">
         <f>G6-H6</f>
         <v>0</v>
       </c>
-      <c r="K6" s="65">
+      <c r="K6" s="63">
         <f>IF(J6&gt;0,J6*2.95%,0)</f>
         <v>0</v>
       </c>
-      <c r="L6" s="66">
+      <c r="L6" s="64">
         <f>O$3*F6%</f>
         <v>45700.000000000007</v>
       </c>
-      <c r="M6" s="66">
+      <c r="M6" s="64">
         <f>O$2*F6%</f>
         <v>457000.00000000006</v>
       </c>
-      <c r="N6" s="67">
-        <v>5000</v>
-      </c>
-      <c r="O6" s="68">
+      <c r="N6" s="65">
+        <v>0</v>
+      </c>
+      <c r="O6" s="66">
         <f t="shared" ref="O6:O33" si="0">ROUND(SUM(J6:N6),0) + Q6</f>
-        <v>507700.01</v>
-      </c>
-      <c r="P6" s="69">
+        <v>502700.01</v>
+      </c>
+      <c r="P6" s="67">
         <f t="shared" ref="P6:P33" si="1">ROUND(O6*3%,0) + O6</f>
-        <v>522931.01</v>
-      </c>
-      <c r="Q6" s="40">
+        <v>517781.01</v>
+      </c>
+      <c r="Q6" s="39">
         <v>0.01</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="55">
+      <c r="B7" s="54">
         <v>2</v>
       </c>
-      <c r="C7" s="55" t="s">
+      <c r="C7" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="55" t="s">
+      <c r="D7" s="54" t="s">
         <v>96</v>
       </c>
-      <c r="E7" s="56"/>
-      <c r="F7" s="61">
+      <c r="E7" s="55"/>
+      <c r="F7" s="59">
         <v>3.07</v>
       </c>
-      <c r="G7" s="62">
-        <v>831391.02</v>
-      </c>
-      <c r="H7" s="63">
-        <v>276300</v>
-      </c>
-      <c r="I7" s="64"/>
-      <c r="J7" s="65">
+      <c r="G7" s="60">
+        <v>909166.02</v>
+      </c>
+      <c r="H7" s="61">
+        <f>177000+307000+160000</f>
+        <v>644000</v>
+      </c>
+      <c r="I7" s="62"/>
+      <c r="J7" s="63">
         <f t="shared" ref="J7:J31" si="2">G7-H7</f>
-        <v>555091.02</v>
-      </c>
-      <c r="K7" s="65">
+        <v>265166.02</v>
+      </c>
+      <c r="K7" s="63">
         <f t="shared" ref="K7:K32" si="3">IF(J7&gt;0,J7*2.95%,0)</f>
-        <v>16375.185090000001</v>
-      </c>
-      <c r="L7" s="66">
+        <v>7822.3975900000014</v>
+      </c>
+      <c r="L7" s="64">
         <f t="shared" ref="L7:L33" si="4">O$3*F7%</f>
         <v>30699.999999999996</v>
       </c>
-      <c r="M7" s="66">
+      <c r="M7" s="64">
         <f t="shared" ref="M7:M33" si="5">O$2*F7%</f>
         <v>307000</v>
       </c>
-      <c r="N7" s="67">
-        <v>0</v>
-      </c>
-      <c r="O7" s="68">
+      <c r="N7" s="65">
+        <v>0</v>
+      </c>
+      <c r="O7" s="66">
         <f t="shared" si="0"/>
-        <v>909166.02</v>
-      </c>
-      <c r="P7" s="69">
+        <v>610688.02</v>
+      </c>
+      <c r="P7" s="67">
         <f t="shared" si="1"/>
-        <v>936441.02</v>
-      </c>
-      <c r="Q7" s="40">
+        <v>629009.02</v>
+      </c>
+      <c r="Q7" s="39">
         <f>Q6+0.01</f>
         <v>0.02</v>
       </c>
-      <c r="R7" s="40" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R7" s="39" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="138">
+      <c r="B8" s="127">
         <v>3</v>
       </c>
-      <c r="C8" s="138" t="s">
+      <c r="C8" s="127" t="s">
         <v>53</v>
       </c>
-      <c r="D8" s="139" t="s">
+      <c r="D8" s="128" t="s">
         <v>146</v>
       </c>
-      <c r="E8" s="140"/>
-      <c r="F8" s="141">
+      <c r="E8" s="129"/>
+      <c r="F8" s="130">
         <v>4.55</v>
       </c>
-      <c r="G8" s="142">
-        <v>409500</v>
-      </c>
-      <c r="H8" s="142">
-        <v>409500</v>
-      </c>
-      <c r="I8" s="143"/>
-      <c r="J8" s="144">
+      <c r="G8" s="131">
+        <v>500500.03</v>
+      </c>
+      <c r="H8" s="131"/>
+      <c r="I8" s="132"/>
+      <c r="J8" s="133">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K8" s="144">
+        <v>500500.03</v>
+      </c>
+      <c r="K8" s="133">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L8" s="145">
+        <v>14764.750885000001</v>
+      </c>
+      <c r="L8" s="134">
         <f t="shared" si="4"/>
         <v>45500</v>
       </c>
-      <c r="M8" s="145">
+      <c r="M8" s="134">
         <f t="shared" si="5"/>
         <v>455000</v>
       </c>
-      <c r="N8" s="146">
-        <v>0</v>
-      </c>
-      <c r="O8" s="147">
+      <c r="N8" s="135">
+        <v>0</v>
+      </c>
+      <c r="O8" s="136">
         <f t="shared" si="0"/>
-        <v>500500.03</v>
-      </c>
-      <c r="P8" s="148">
+        <v>1015765.03</v>
+      </c>
+      <c r="P8" s="137">
         <f t="shared" si="1"/>
-        <v>515515.03</v>
-      </c>
-      <c r="Q8" s="40">
+        <v>1046238.03</v>
+      </c>
+      <c r="Q8" s="39">
         <f t="shared" ref="Q8:Q32" si="6">Q7+0.01</f>
         <v>0.03</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="55">
+      <c r="B9" s="54">
         <v>4</v>
       </c>
-      <c r="C9" s="55" t="s">
+      <c r="C9" s="54" t="s">
         <v>54</v>
       </c>
-      <c r="D9" s="55" t="s">
+      <c r="D9" s="54" t="s">
         <v>97</v>
       </c>
-      <c r="E9" s="56"/>
-      <c r="F9" s="61">
+      <c r="E9" s="55"/>
+      <c r="F9" s="59">
         <v>3.05</v>
       </c>
-      <c r="G9" s="62">
-        <v>360126.04</v>
-      </c>
-      <c r="H9" s="63">
-        <v>400000</v>
-      </c>
-      <c r="I9" s="64"/>
-      <c r="J9" s="65">
+      <c r="G9" s="60">
+        <v>304495.03999999998</v>
+      </c>
+      <c r="H9" s="61">
+        <v>325500.03999999998</v>
+      </c>
+      <c r="I9" s="62"/>
+      <c r="J9" s="63">
         <f t="shared" si="2"/>
-        <v>-39873.960000000021</v>
-      </c>
-      <c r="K9" s="65">
+        <v>-21005</v>
+      </c>
+      <c r="K9" s="63">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L9" s="66">
+      <c r="L9" s="64">
         <f t="shared" si="4"/>
         <v>30500</v>
       </c>
-      <c r="M9" s="66">
+      <c r="M9" s="64">
         <f t="shared" si="5"/>
         <v>305000</v>
       </c>
-      <c r="N9" s="67">
-        <v>0</v>
-      </c>
-      <c r="O9" s="68">
+      <c r="N9" s="65">
+        <v>0</v>
+      </c>
+      <c r="O9" s="66">
         <f t="shared" si="0"/>
-        <v>295626.03999999998</v>
-      </c>
-      <c r="P9" s="69">
+        <v>314495.03999999998</v>
+      </c>
+      <c r="P9" s="67">
         <f t="shared" si="1"/>
-        <v>304495.03999999998</v>
-      </c>
-      <c r="Q9" s="40">
+        <v>323930.03999999998</v>
+      </c>
+      <c r="Q9" s="39">
         <f t="shared" si="6"/>
         <v>0.04</v>
       </c>
       <c r="R9" t="s">
         <v>141</v>
       </c>
-      <c r="S9" s="40"/>
-    </row>
-    <row r="10" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S9" s="39"/>
+    </row>
+    <row r="10" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="55">
+      <c r="B10" s="54">
         <v>5</v>
       </c>
-      <c r="C10" s="55" t="s">
+      <c r="C10" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="D10" s="55" t="s">
+      <c r="D10" s="54" t="s">
         <v>98</v>
       </c>
-      <c r="E10" s="56"/>
-      <c r="F10" s="61">
+      <c r="E10" s="55"/>
+      <c r="F10" s="59">
         <v>4.55</v>
       </c>
-      <c r="G10" s="62">
-        <v>454348.05</v>
-      </c>
-      <c r="H10" s="63">
-        <v>460000</v>
-      </c>
-      <c r="I10" s="64"/>
-      <c r="J10" s="65">
+      <c r="G10" s="60">
+        <v>509693.05</v>
+      </c>
+      <c r="H10" s="61">
+        <f>400000+95000</f>
+        <v>495000</v>
+      </c>
+      <c r="I10" s="62"/>
+      <c r="J10" s="63">
         <f t="shared" si="2"/>
-        <v>-5651.9500000000116</v>
-      </c>
-      <c r="K10" s="65">
+        <v>14693.049999999988</v>
+      </c>
+      <c r="K10" s="63">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L10" s="66">
+        <v>433.44497499999966</v>
+      </c>
+      <c r="L10" s="64">
         <f t="shared" si="4"/>
         <v>45500</v>
       </c>
-      <c r="M10" s="66">
+      <c r="M10" s="64">
         <f t="shared" si="5"/>
         <v>455000</v>
       </c>
-      <c r="N10" s="67">
-        <v>0</v>
-      </c>
-      <c r="O10" s="68">
+      <c r="N10" s="65">
+        <v>0</v>
+      </c>
+      <c r="O10" s="66">
         <f t="shared" si="0"/>
-        <v>494848.05</v>
-      </c>
-      <c r="P10" s="69">
+        <v>515626.05</v>
+      </c>
+      <c r="P10" s="67">
         <f t="shared" si="1"/>
-        <v>509693.05</v>
-      </c>
-      <c r="Q10" s="40">
+        <v>531095.05000000005</v>
+      </c>
+      <c r="Q10" s="39">
         <f t="shared" si="6"/>
         <v>0.05</v>
       </c>
-      <c r="S10" s="40"/>
-    </row>
-    <row r="11" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S10" s="39"/>
+    </row>
+    <row r="11" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="55">
+      <c r="B11" s="54">
         <v>6</v>
       </c>
-      <c r="C11" s="55" t="s">
+      <c r="C11" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="55" t="s">
+      <c r="D11" s="54" t="s">
         <v>99</v>
       </c>
-      <c r="E11" s="55"/>
-      <c r="F11" s="61">
+      <c r="E11" s="54"/>
+      <c r="F11" s="59">
         <v>3.05</v>
       </c>
-      <c r="G11" s="62">
-        <v>305000.06</v>
-      </c>
-      <c r="H11" s="63">
-        <v>314150.06</v>
-      </c>
-      <c r="I11" s="64"/>
-      <c r="J11" s="65">
+      <c r="G11" s="60">
+        <v>326350.06</v>
+      </c>
+      <c r="H11" s="61">
+        <f>G11</f>
+        <v>326350.06</v>
+      </c>
+      <c r="I11" s="62"/>
+      <c r="J11" s="63">
         <f t="shared" si="2"/>
-        <v>-9150</v>
-      </c>
-      <c r="K11" s="65">
+        <v>0</v>
+      </c>
+      <c r="K11" s="63">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L11" s="66">
+      <c r="L11" s="64">
         <f t="shared" si="4"/>
         <v>30500</v>
       </c>
-      <c r="M11" s="66">
+      <c r="M11" s="64">
         <f t="shared" si="5"/>
         <v>305000</v>
       </c>
-      <c r="N11" s="67">
-        <v>0</v>
-      </c>
-      <c r="O11" s="68">
+      <c r="N11" s="65">
+        <v>0</v>
+      </c>
+      <c r="O11" s="66">
         <f t="shared" si="0"/>
-        <v>326350.06</v>
-      </c>
-      <c r="P11" s="69">
+        <v>335500.06</v>
+      </c>
+      <c r="P11" s="67">
         <f t="shared" si="1"/>
-        <v>336141.06</v>
-      </c>
-      <c r="Q11" s="40">
+        <v>345565.06</v>
+      </c>
+      <c r="Q11" s="39">
         <f t="shared" si="6"/>
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="55">
+      <c r="B12" s="54">
         <v>7</v>
       </c>
-      <c r="C12" s="125" t="s">
+      <c r="C12" s="119" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="125" t="s">
+      <c r="D12" s="119" t="s">
         <v>100</v>
       </c>
-      <c r="E12" s="55"/>
-      <c r="F12" s="61">
+      <c r="E12" s="54"/>
+      <c r="F12" s="59">
         <v>4.55</v>
       </c>
-      <c r="G12" s="62">
-        <v>455000.07</v>
-      </c>
-      <c r="H12" s="63">
-        <f>240000+205000+4000+10000</f>
-        <v>459000</v>
-      </c>
-      <c r="I12" s="64"/>
-      <c r="J12" s="65">
+      <c r="G12" s="60">
+        <v>496500.07</v>
+      </c>
+      <c r="H12" s="61"/>
+      <c r="I12" s="62"/>
+      <c r="J12" s="63">
         <f t="shared" si="2"/>
-        <v>-3999.929999999993</v>
-      </c>
-      <c r="K12" s="65">
+        <v>496500.07</v>
+      </c>
+      <c r="K12" s="63">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L12" s="66">
+        <v>14646.752065000001</v>
+      </c>
+      <c r="L12" s="64">
         <f t="shared" si="4"/>
         <v>45500</v>
       </c>
-      <c r="M12" s="66">
+      <c r="M12" s="64">
         <f t="shared" si="5"/>
         <v>455000</v>
       </c>
-      <c r="N12" s="67">
-        <v>0</v>
-      </c>
-      <c r="O12" s="68">
+      <c r="N12" s="65">
+        <v>0</v>
+      </c>
+      <c r="O12" s="66">
         <f t="shared" si="0"/>
-        <v>496500.07</v>
-      </c>
-      <c r="P12" s="69">
+        <v>1011647.07</v>
+      </c>
+      <c r="P12" s="67">
         <f t="shared" si="1"/>
-        <v>511395.07</v>
-      </c>
-      <c r="Q12" s="40">
+        <v>1041996.07</v>
+      </c>
+      <c r="Q12" s="39">
         <f t="shared" si="6"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="R12" s="121"/>
-      <c r="S12" s="119"/>
-    </row>
-    <row r="13" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R12" s="117"/>
+      <c r="S12" s="116"/>
+    </row>
+    <row r="13" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="55">
+      <c r="B13" s="54">
         <v>8</v>
       </c>
-      <c r="C13" s="55" t="s">
+      <c r="C13" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="D13" s="55" t="s">
+      <c r="D13" s="54" t="s">
         <v>101</v>
       </c>
-      <c r="E13" s="56"/>
-      <c r="F13" s="61">
+      <c r="E13" s="55"/>
+      <c r="F13" s="59">
         <v>3.05</v>
       </c>
-      <c r="G13" s="62">
-        <v>296939.08</v>
-      </c>
-      <c r="H13" s="63">
-        <v>305847</v>
-      </c>
-      <c r="I13" s="64"/>
-      <c r="J13" s="65">
+      <c r="G13" s="60">
+        <v>326592.08</v>
+      </c>
+      <c r="H13" s="61">
+        <v>336390.08</v>
+      </c>
+      <c r="I13" s="62"/>
+      <c r="J13" s="63">
         <f t="shared" si="2"/>
-        <v>-8907.9199999999837</v>
-      </c>
-      <c r="K13" s="65">
+        <v>-9798</v>
+      </c>
+      <c r="K13" s="63">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L13" s="66">
+      <c r="L13" s="64">
         <f t="shared" si="4"/>
         <v>30500</v>
       </c>
-      <c r="M13" s="66">
+      <c r="M13" s="64">
         <f t="shared" si="5"/>
         <v>305000</v>
       </c>
-      <c r="N13" s="67">
-        <v>0</v>
-      </c>
-      <c r="O13" s="68">
+      <c r="N13" s="65">
+        <v>0</v>
+      </c>
+      <c r="O13" s="66">
         <f t="shared" si="0"/>
-        <v>326592.08</v>
-      </c>
-      <c r="P13" s="69">
+        <v>325702.08</v>
+      </c>
+      <c r="P13" s="67">
         <f t="shared" si="1"/>
-        <v>336390.08</v>
-      </c>
-      <c r="Q13" s="40">
+        <v>335473.08</v>
+      </c>
+      <c r="Q13" s="39">
         <f t="shared" si="6"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="55">
+      <c r="B14" s="54">
         <v>9</v>
       </c>
-      <c r="C14" s="55" t="s">
+      <c r="C14" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="D14" s="55" t="s">
+      <c r="D14" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="E14" s="56"/>
-      <c r="F14" s="61">
+      <c r="E14" s="55"/>
+      <c r="F14" s="59">
         <v>4.5599999999999996</v>
       </c>
-      <c r="G14" s="62">
-        <v>455600.09</v>
-      </c>
-      <c r="H14" s="127">
-        <v>470000</v>
-      </c>
-      <c r="I14" s="64"/>
-      <c r="J14" s="65">
+      <c r="G14" s="60">
+        <v>487200.09</v>
+      </c>
+      <c r="H14" s="155">
+        <v>490000</v>
+      </c>
+      <c r="I14" s="62"/>
+      <c r="J14" s="63">
         <f t="shared" si="2"/>
-        <v>-14399.909999999974</v>
-      </c>
-      <c r="K14" s="65">
+        <v>-2799.9099999999744</v>
+      </c>
+      <c r="K14" s="63">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L14" s="66">
+      <c r="L14" s="64">
         <f t="shared" si="4"/>
         <v>45599.999999999993</v>
       </c>
-      <c r="M14" s="66">
+      <c r="M14" s="64">
         <f t="shared" si="5"/>
         <v>455999.99999999994</v>
       </c>
-      <c r="N14" s="67">
-        <v>0</v>
-      </c>
-      <c r="O14" s="68">
+      <c r="N14" s="65">
+        <v>0</v>
+      </c>
+      <c r="O14" s="66">
         <f t="shared" si="0"/>
-        <v>487200.09</v>
-      </c>
-      <c r="P14" s="69">
+        <v>498800.09</v>
+      </c>
+      <c r="P14" s="67">
         <f t="shared" si="1"/>
-        <v>501816.09</v>
-      </c>
-      <c r="Q14" s="40">
+        <v>513764.09</v>
+      </c>
+      <c r="Q14" s="39">
         <f t="shared" si="6"/>
         <v>0.09</v>
       </c>
@@ -3670,633 +3608,630 @@
         <v>149</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="55">
+      <c r="B15" s="54">
         <v>10</v>
       </c>
-      <c r="C15" s="55" t="s">
+      <c r="C15" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="55" t="s">
+      <c r="D15" s="54" t="s">
         <v>103</v>
       </c>
-      <c r="E15" s="56"/>
-      <c r="F15" s="61">
+      <c r="E15" s="55"/>
+      <c r="F15" s="59">
         <v>3.05</v>
       </c>
-      <c r="G15" s="62">
-        <v>305443.09999999998</v>
-      </c>
-      <c r="H15" s="63">
+      <c r="G15" s="60">
+        <v>335500.09999999998</v>
+      </c>
+      <c r="H15" s="61">
         <f>G15</f>
-        <v>305443.09999999998</v>
-      </c>
-      <c r="I15" s="64"/>
-      <c r="J15" s="65">
+        <v>335500.09999999998</v>
+      </c>
+      <c r="I15" s="62"/>
+      <c r="J15" s="63">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K15" s="65">
+      <c r="K15" s="63">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L15" s="66">
+      <c r="L15" s="64">
         <f t="shared" si="4"/>
         <v>30500</v>
       </c>
-      <c r="M15" s="66">
+      <c r="M15" s="64">
         <f t="shared" si="5"/>
         <v>305000</v>
       </c>
-      <c r="N15" s="67">
-        <v>0</v>
-      </c>
-      <c r="O15" s="68">
+      <c r="N15" s="65">
+        <v>0</v>
+      </c>
+      <c r="O15" s="66">
         <f t="shared" si="0"/>
         <v>335500.09999999998</v>
       </c>
-      <c r="P15" s="69">
+      <c r="P15" s="67">
         <f t="shared" si="1"/>
         <v>345565.1</v>
       </c>
-      <c r="Q15" s="40">
+      <c r="Q15" s="39">
         <f t="shared" si="6"/>
         <v>9.9999999999999992E-2</v>
       </c>
       <c r="R15" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="55">
+      <c r="B16" s="54">
         <v>11</v>
       </c>
-      <c r="C16" s="55" t="s">
+      <c r="C16" s="54" t="s">
         <v>61</v>
       </c>
-      <c r="D16" s="55" t="s">
+      <c r="D16" s="54" t="s">
         <v>104</v>
       </c>
-      <c r="E16" s="56"/>
-      <c r="F16" s="61">
+      <c r="E16" s="55"/>
+      <c r="F16" s="59">
         <v>4.55</v>
       </c>
-      <c r="G16" s="62">
-        <v>455000.11</v>
-      </c>
-      <c r="H16" s="63">
-        <f>G16</f>
-        <v>455000.11</v>
-      </c>
-      <c r="I16" s="64"/>
-      <c r="J16" s="65">
+      <c r="G16" s="60">
+        <v>500500.11</v>
+      </c>
+      <c r="H16" s="61">
+        <v>515515.11</v>
+      </c>
+      <c r="I16" s="62"/>
+      <c r="J16" s="63">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="65">
+        <v>-15015</v>
+      </c>
+      <c r="K16" s="63">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L16" s="66">
+      <c r="L16" s="64">
         <f t="shared" si="4"/>
         <v>45500</v>
       </c>
-      <c r="M16" s="66">
+      <c r="M16" s="64">
         <f t="shared" si="5"/>
         <v>455000</v>
       </c>
-      <c r="N16" s="67">
-        <v>0</v>
-      </c>
-      <c r="O16" s="68">
+      <c r="N16" s="65">
+        <v>0</v>
+      </c>
+      <c r="O16" s="66">
         <f t="shared" si="0"/>
-        <v>500500.11</v>
-      </c>
-      <c r="P16" s="69">
+        <v>485485.11</v>
+      </c>
+      <c r="P16" s="67">
         <f t="shared" si="1"/>
-        <v>515515.11</v>
-      </c>
-      <c r="Q16" s="40">
+        <v>500050.11</v>
+      </c>
+      <c r="Q16" s="39">
         <f t="shared" si="6"/>
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="55">
+      <c r="B17" s="54">
         <v>12</v>
       </c>
-      <c r="C17" s="55" t="s">
+      <c r="C17" s="54" t="s">
         <v>62</v>
       </c>
-      <c r="D17" s="55" t="s">
+      <c r="D17" s="54" t="s">
         <v>105</v>
       </c>
-      <c r="E17" s="56"/>
-      <c r="F17" s="61">
+      <c r="E17" s="55"/>
+      <c r="F17" s="59">
         <v>3.05</v>
       </c>
-      <c r="G17" s="62">
-        <v>587598.12</v>
-      </c>
-      <c r="H17" s="63">
-        <v>214500</v>
-      </c>
-      <c r="I17" s="64"/>
-      <c r="J17" s="65">
+      <c r="G17" s="60">
+        <v>719605.12</v>
+      </c>
+      <c r="H17" s="61">
+        <v>305000</v>
+      </c>
+      <c r="I17" s="62"/>
+      <c r="J17" s="63">
         <f t="shared" si="2"/>
-        <v>373098.12</v>
-      </c>
-      <c r="K17" s="65">
+        <v>414605.12</v>
+      </c>
+      <c r="K17" s="63">
         <f t="shared" si="3"/>
-        <v>11006.394540000001</v>
-      </c>
-      <c r="L17" s="66">
+        <v>12230.851040000001</v>
+      </c>
+      <c r="L17" s="64">
         <f t="shared" si="4"/>
         <v>30500</v>
       </c>
-      <c r="M17" s="66">
+      <c r="M17" s="64">
         <f t="shared" si="5"/>
         <v>305000</v>
       </c>
-      <c r="N17" s="67">
-        <v>0</v>
-      </c>
-      <c r="O17" s="68">
+      <c r="N17" s="65">
+        <v>0</v>
+      </c>
+      <c r="O17" s="66">
         <f t="shared" si="0"/>
-        <v>719605.12</v>
-      </c>
-      <c r="P17" s="69">
+        <v>762336.12</v>
+      </c>
+      <c r="P17" s="67">
         <f t="shared" si="1"/>
-        <v>741193.12</v>
-      </c>
-      <c r="Q17" s="40">
+        <v>785206.12</v>
+      </c>
+      <c r="Q17" s="39">
         <f t="shared" si="6"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="55">
+      <c r="B18" s="54">
         <v>13</v>
       </c>
-      <c r="C18" s="55" t="s">
+      <c r="C18" s="54" t="s">
         <v>63</v>
       </c>
-      <c r="D18" s="55" t="s">
+      <c r="D18" s="54" t="s">
         <v>106</v>
       </c>
-      <c r="E18" s="56"/>
-      <c r="F18" s="61">
+      <c r="E18" s="55"/>
+      <c r="F18" s="59">
         <v>4.55</v>
       </c>
-      <c r="G18" s="62">
-        <v>442993.13</v>
-      </c>
-      <c r="H18" s="63">
-        <v>456283.13</v>
-      </c>
-      <c r="I18" s="64"/>
-      <c r="J18" s="65">
+      <c r="G18" s="60">
+        <v>487210.13</v>
+      </c>
+      <c r="H18" s="61">
+        <f>G18</f>
+        <v>487210.13</v>
+      </c>
+      <c r="I18" s="62"/>
+      <c r="J18" s="63">
         <f t="shared" si="2"/>
-        <v>-13290</v>
-      </c>
-      <c r="K18" s="65">
+        <v>0</v>
+      </c>
+      <c r="K18" s="63">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L18" s="66">
+      <c r="L18" s="64">
         <f t="shared" si="4"/>
         <v>45500</v>
       </c>
-      <c r="M18" s="66">
+      <c r="M18" s="64">
         <f t="shared" si="5"/>
         <v>455000</v>
       </c>
-      <c r="N18" s="67">
-        <v>0</v>
-      </c>
-      <c r="O18" s="68">
+      <c r="N18" s="65">
+        <v>0</v>
+      </c>
+      <c r="O18" s="66">
         <f t="shared" si="0"/>
-        <v>487210.13</v>
-      </c>
-      <c r="P18" s="69">
+        <v>500500.13</v>
+      </c>
+      <c r="P18" s="67">
         <f t="shared" si="1"/>
-        <v>501826.13</v>
-      </c>
-      <c r="Q18" s="40">
+        <v>515515.13</v>
+      </c>
+      <c r="Q18" s="39">
         <f t="shared" si="6"/>
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="55">
+      <c r="B19" s="54">
         <v>14</v>
       </c>
-      <c r="C19" s="55" t="s">
+      <c r="C19" s="54" t="s">
         <v>64</v>
       </c>
-      <c r="D19" s="55" t="s">
+      <c r="D19" s="54" t="s">
         <v>107</v>
       </c>
-      <c r="E19" s="56"/>
-      <c r="F19" s="61">
+      <c r="E19" s="55"/>
+      <c r="F19" s="59">
         <v>3.18</v>
       </c>
-      <c r="G19" s="62">
-        <v>318000.14</v>
-      </c>
-      <c r="H19" s="63">
+      <c r="G19" s="60">
+        <v>349800.14</v>
+      </c>
+      <c r="H19" s="61">
         <f>G19</f>
-        <v>318000.14</v>
-      </c>
-      <c r="I19" s="64"/>
-      <c r="J19" s="65">
+        <v>349800.14</v>
+      </c>
+      <c r="I19" s="62"/>
+      <c r="J19" s="63">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K19" s="65">
+      <c r="K19" s="63">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L19" s="66">
+      <c r="L19" s="64">
         <f t="shared" si="4"/>
         <v>31800.000000000004</v>
       </c>
-      <c r="M19" s="66">
+      <c r="M19" s="64">
         <f t="shared" si="5"/>
         <v>318000</v>
       </c>
-      <c r="N19" s="67">
-        <v>0</v>
-      </c>
-      <c r="O19" s="68">
+      <c r="N19" s="65">
+        <v>0</v>
+      </c>
+      <c r="O19" s="66">
         <f t="shared" si="0"/>
         <v>349800.14</v>
       </c>
-      <c r="P19" s="69">
+      <c r="P19" s="67">
         <f t="shared" si="1"/>
         <v>360294.14</v>
       </c>
-      <c r="Q19" s="40">
+      <c r="Q19" s="39">
         <f t="shared" si="6"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="55">
+      <c r="B20" s="54">
         <v>15</v>
       </c>
-      <c r="C20" s="55" t="s">
+      <c r="C20" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="D20" s="55" t="s">
+      <c r="D20" s="54" t="s">
         <v>108</v>
       </c>
-      <c r="E20" s="56"/>
-      <c r="F20" s="61">
+      <c r="E20" s="55"/>
+      <c r="F20" s="59">
         <v>4.55</v>
       </c>
-      <c r="G20" s="62">
-        <v>455000.15</v>
-      </c>
-      <c r="H20" s="63">
+      <c r="G20" s="60">
+        <v>500500.15</v>
+      </c>
+      <c r="H20" s="61">
         <f>G20</f>
-        <v>455000.15</v>
-      </c>
-      <c r="I20" s="64"/>
-      <c r="J20" s="65">
+        <v>500500.15</v>
+      </c>
+      <c r="I20" s="62"/>
+      <c r="J20" s="63">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K20" s="65">
+      <c r="K20" s="63">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L20" s="66">
+      <c r="L20" s="64">
         <f t="shared" si="4"/>
         <v>45500</v>
       </c>
-      <c r="M20" s="66">
+      <c r="M20" s="64">
         <f t="shared" si="5"/>
         <v>455000</v>
       </c>
-      <c r="N20" s="67">
-        <v>0</v>
-      </c>
-      <c r="O20" s="68">
+      <c r="N20" s="65">
+        <v>0</v>
+      </c>
+      <c r="O20" s="66">
         <f t="shared" si="0"/>
         <v>500500.15</v>
       </c>
-      <c r="P20" s="69">
+      <c r="P20" s="67">
         <f t="shared" si="1"/>
         <v>515515.15</v>
       </c>
-      <c r="Q20" s="40">
+      <c r="Q20" s="39">
         <f t="shared" si="6"/>
         <v>0.15</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="55">
+      <c r="B21" s="54">
         <v>16</v>
       </c>
-      <c r="C21" s="55" t="s">
+      <c r="C21" s="54" t="s">
         <v>66</v>
       </c>
-      <c r="D21" s="55" t="s">
+      <c r="D21" s="54" t="s">
         <v>109</v>
       </c>
-      <c r="E21" s="55"/>
-      <c r="F21" s="61">
+      <c r="E21" s="54"/>
+      <c r="F21" s="59">
         <v>3.17</v>
       </c>
-      <c r="G21" s="62">
-        <v>308200.15999999997</v>
-      </c>
-      <c r="H21" s="63">
-        <v>317446</v>
-      </c>
-      <c r="I21" s="64"/>
-      <c r="J21" s="65">
+      <c r="G21" s="60">
+        <v>339454.16</v>
+      </c>
+      <c r="H21" s="61">
+        <v>340000</v>
+      </c>
+      <c r="I21" s="62"/>
+      <c r="J21" s="63">
         <f t="shared" si="2"/>
-        <v>-9245.8400000000256</v>
-      </c>
-      <c r="K21" s="65">
+        <v>-545.84000000002561</v>
+      </c>
+      <c r="K21" s="63">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L21" s="66">
+      <c r="L21" s="64">
         <f t="shared" si="4"/>
         <v>31700</v>
       </c>
-      <c r="M21" s="66">
+      <c r="M21" s="64">
         <f t="shared" si="5"/>
         <v>317000</v>
       </c>
-      <c r="N21" s="67">
-        <v>0</v>
-      </c>
-      <c r="O21" s="68">
+      <c r="N21" s="65">
+        <v>0</v>
+      </c>
+      <c r="O21" s="66">
         <f t="shared" si="0"/>
-        <v>339454.16</v>
-      </c>
-      <c r="P21" s="69">
+        <v>348154.16</v>
+      </c>
+      <c r="P21" s="67">
         <f t="shared" si="1"/>
-        <v>349638.16</v>
-      </c>
-      <c r="Q21" s="40">
+        <v>358599.16</v>
+      </c>
+      <c r="Q21" s="39">
         <f t="shared" si="6"/>
         <v>0.16</v>
       </c>
       <c r="R21" t="s">
-        <v>151</v>
-      </c>
-      <c r="S21" s="39"/>
-    </row>
-    <row r="22" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>150</v>
+      </c>
+      <c r="S21" s="38"/>
+    </row>
+    <row r="22" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="55">
+      <c r="B22" s="54">
         <v>17</v>
       </c>
-      <c r="C22" s="55" t="s">
+      <c r="C22" s="54" t="s">
         <v>67</v>
       </c>
-      <c r="D22" s="55" t="s">
+      <c r="D22" s="54" t="s">
         <v>110</v>
       </c>
-      <c r="E22" s="56"/>
-      <c r="F22" s="61">
+      <c r="E22" s="55"/>
+      <c r="F22" s="59">
         <v>4.55</v>
       </c>
-      <c r="G22" s="63">
-        <v>455000.17</v>
-      </c>
-      <c r="H22" s="63">
-        <f>G22</f>
-        <v>455000.17</v>
-      </c>
-      <c r="I22" s="64"/>
-      <c r="J22" s="65">
+      <c r="G22" s="61">
+        <v>500500.17</v>
+      </c>
+      <c r="H22" s="61"/>
+      <c r="I22" s="62"/>
+      <c r="J22" s="63">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K22" s="65">
+        <v>500500.17</v>
+      </c>
+      <c r="K22" s="63">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L22" s="66">
+        <v>14764.755015000001</v>
+      </c>
+      <c r="L22" s="64">
         <f t="shared" si="4"/>
         <v>45500</v>
       </c>
-      <c r="M22" s="66">
+      <c r="M22" s="64">
         <f t="shared" si="5"/>
         <v>455000</v>
       </c>
-      <c r="N22" s="67">
-        <v>0</v>
-      </c>
-      <c r="O22" s="68">
+      <c r="N22" s="65">
+        <v>0</v>
+      </c>
+      <c r="O22" s="66">
         <f t="shared" si="0"/>
-        <v>500500.17</v>
-      </c>
-      <c r="P22" s="69">
+        <v>1015765.17</v>
+      </c>
+      <c r="P22" s="67">
         <f t="shared" si="1"/>
-        <v>515515.17</v>
-      </c>
-      <c r="Q22" s="40">
+        <v>1046238.17</v>
+      </c>
+      <c r="Q22" s="39">
         <f t="shared" si="6"/>
         <v>0.17</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="55">
+      <c r="B23" s="54">
         <v>18</v>
       </c>
-      <c r="C23" s="55" t="s">
+      <c r="C23" s="54" t="s">
         <v>68</v>
       </c>
-      <c r="D23" s="55" t="s">
+      <c r="D23" s="54" t="s">
         <v>111</v>
       </c>
-      <c r="E23" s="55"/>
-      <c r="F23" s="61">
+      <c r="E23" s="54"/>
+      <c r="F23" s="59">
         <v>3.17</v>
       </c>
-      <c r="G23" s="62">
-        <v>308441.18</v>
-      </c>
-      <c r="H23" s="63">
+      <c r="G23" s="60">
+        <v>348700.18</v>
+      </c>
+      <c r="H23" s="61">
         <f>G23</f>
-        <v>308441.18</v>
-      </c>
-      <c r="I23" s="64"/>
-      <c r="J23" s="65">
+        <v>348700.18</v>
+      </c>
+      <c r="I23" s="62"/>
+      <c r="J23" s="63">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K23" s="65">
+      <c r="K23" s="63">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L23" s="66">
+      <c r="L23" s="64">
         <f t="shared" si="4"/>
         <v>31700</v>
       </c>
-      <c r="M23" s="66">
+      <c r="M23" s="64">
         <f t="shared" si="5"/>
         <v>317000</v>
       </c>
-      <c r="N23" s="67">
-        <v>0</v>
-      </c>
-      <c r="O23" s="68">
+      <c r="N23" s="65">
+        <v>0</v>
+      </c>
+      <c r="O23" s="66">
         <f t="shared" si="0"/>
         <v>348700.18</v>
       </c>
-      <c r="P23" s="69">
+      <c r="P23" s="67">
         <f t="shared" si="1"/>
         <v>359161.18</v>
       </c>
-      <c r="Q23" s="40">
+      <c r="Q23" s="39">
         <f t="shared" si="6"/>
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="55">
+      <c r="B24" s="54">
         <v>19</v>
       </c>
-      <c r="C24" s="55" t="s">
+      <c r="C24" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="D24" s="55" t="s">
+      <c r="D24" s="54" t="s">
         <v>112</v>
       </c>
-      <c r="E24" s="56"/>
-      <c r="F24" s="61">
+      <c r="E24" s="55"/>
+      <c r="F24" s="59">
         <v>4.55</v>
       </c>
-      <c r="G24" s="62">
-        <v>455000.19</v>
-      </c>
-      <c r="H24" s="63">
+      <c r="G24" s="60">
+        <v>515515.19</v>
+      </c>
+      <c r="H24" s="61">
         <f>G24</f>
-        <v>455000.19</v>
-      </c>
-      <c r="I24" s="64"/>
-      <c r="J24" s="65">
+        <v>515515.19</v>
+      </c>
+      <c r="I24" s="62"/>
+      <c r="J24" s="63">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K24" s="65">
+      <c r="K24" s="63">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L24" s="66">
+      <c r="L24" s="64">
         <f t="shared" si="4"/>
         <v>45500</v>
       </c>
-      <c r="M24" s="66">
+      <c r="M24" s="64">
         <f t="shared" si="5"/>
         <v>455000</v>
       </c>
-      <c r="N24" s="67">
-        <v>0</v>
-      </c>
-      <c r="O24" s="68">
+      <c r="N24" s="65">
+        <v>0</v>
+      </c>
+      <c r="O24" s="66">
         <f t="shared" si="0"/>
         <v>500500.19</v>
       </c>
-      <c r="P24" s="69">
+      <c r="P24" s="67">
         <f t="shared" si="1"/>
         <v>515515.19</v>
       </c>
-      <c r="Q24" s="40">
+      <c r="Q24" s="39">
         <f t="shared" si="6"/>
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B25" s="55">
+      <c r="B25" s="54">
         <v>20</v>
       </c>
-      <c r="C25" s="55" t="s">
+      <c r="C25" s="54" t="s">
         <v>70</v>
       </c>
-      <c r="D25" s="55" t="s">
+      <c r="D25" s="54" t="s">
         <v>113</v>
       </c>
-      <c r="E25" s="55"/>
-      <c r="F25" s="61">
+      <c r="E25" s="54"/>
+      <c r="F25" s="59">
         <v>3.17</v>
       </c>
-      <c r="G25" s="63">
-        <v>317000.2</v>
-      </c>
-      <c r="H25" s="63">
+      <c r="G25" s="61">
+        <v>348700.2</v>
+      </c>
+      <c r="H25" s="61">
         <f>G25</f>
-        <v>317000.2</v>
-      </c>
-      <c r="I25" s="64"/>
-      <c r="J25" s="65">
+        <v>348700.2</v>
+      </c>
+      <c r="I25" s="62"/>
+      <c r="J25" s="63">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K25" s="65">
+      <c r="K25" s="63">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L25" s="66">
+      <c r="L25" s="64">
         <f t="shared" si="4"/>
         <v>31700</v>
       </c>
-      <c r="M25" s="66">
+      <c r="M25" s="64">
         <f t="shared" si="5"/>
         <v>317000</v>
       </c>
-      <c r="N25" s="67">
-        <v>0</v>
-      </c>
-      <c r="O25" s="68">
+      <c r="N25" s="65">
+        <v>0</v>
+      </c>
+      <c r="O25" s="66">
         <f t="shared" si="0"/>
         <v>348700.2</v>
       </c>
-      <c r="P25" s="69">
+      <c r="P25" s="67">
         <f t="shared" si="1"/>
         <v>359161.2</v>
       </c>
-      <c r="Q25" s="40">
+      <c r="Q25" s="39">
         <f t="shared" si="6"/>
         <v>0.20000000000000004</v>
       </c>
@@ -4304,286 +4239,286 @@
         <v>139</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B26" s="55">
+      <c r="B26" s="54">
         <v>21</v>
       </c>
-      <c r="C26" s="55" t="s">
+      <c r="C26" s="54" t="s">
         <v>71</v>
       </c>
-      <c r="D26" s="55" t="s">
+      <c r="D26" s="54" t="s">
         <v>114</v>
       </c>
-      <c r="E26" s="56"/>
-      <c r="F26" s="61">
+      <c r="E26" s="55"/>
+      <c r="F26" s="59">
         <v>4.55</v>
       </c>
-      <c r="G26" s="62">
-        <v>455000.21</v>
-      </c>
-      <c r="H26" s="128">
+      <c r="G26" s="60">
+        <v>500500.21</v>
+      </c>
+      <c r="H26" s="61">
         <f>G26</f>
-        <v>455000.21</v>
-      </c>
-      <c r="I26" s="64"/>
-      <c r="J26" s="65">
+        <v>500500.21</v>
+      </c>
+      <c r="I26" s="62"/>
+      <c r="J26" s="63">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K26" s="65">
+      <c r="K26" s="63">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L26" s="66">
+      <c r="L26" s="64">
         <f t="shared" si="4"/>
         <v>45500</v>
       </c>
-      <c r="M26" s="66">
+      <c r="M26" s="64">
         <f t="shared" si="5"/>
         <v>455000</v>
       </c>
-      <c r="N26" s="67">
-        <v>0</v>
-      </c>
-      <c r="O26" s="68">
+      <c r="N26" s="65">
+        <v>0</v>
+      </c>
+      <c r="O26" s="66">
         <f t="shared" si="0"/>
         <v>500500.21</v>
       </c>
-      <c r="P26" s="69">
+      <c r="P26" s="67">
         <f t="shared" si="1"/>
         <v>515515.21</v>
       </c>
-      <c r="Q26" s="40">
+      <c r="Q26" s="39">
         <f t="shared" si="6"/>
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B27" s="55">
+      <c r="B27" s="54">
         <v>22</v>
       </c>
-      <c r="C27" s="55" t="s">
+      <c r="C27" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="D27" s="55" t="s">
+      <c r="D27" s="54" t="s">
         <v>115</v>
       </c>
-      <c r="E27" s="56"/>
-      <c r="F27" s="61">
+      <c r="E27" s="55"/>
+      <c r="F27" s="59">
         <v>3.17</v>
       </c>
-      <c r="G27" s="62">
-        <v>-102449.78</v>
-      </c>
-      <c r="H27" s="63">
+      <c r="G27" s="60">
+        <v>-135619.78</v>
+      </c>
+      <c r="H27" s="61">
         <f>381870.22</f>
         <v>381870.22</v>
       </c>
-      <c r="I27" s="64"/>
-      <c r="J27" s="65">
+      <c r="I27" s="62"/>
+      <c r="J27" s="63">
         <f t="shared" si="2"/>
-        <v>-484320</v>
-      </c>
-      <c r="K27" s="65">
+        <v>-517490</v>
+      </c>
+      <c r="K27" s="63">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L27" s="66">
+      <c r="L27" s="64">
         <f t="shared" si="4"/>
         <v>31700</v>
       </c>
-      <c r="M27" s="66">
+      <c r="M27" s="64">
         <f t="shared" si="5"/>
         <v>317000</v>
       </c>
-      <c r="N27" s="67">
-        <v>0</v>
-      </c>
-      <c r="O27" s="68">
+      <c r="N27" s="65">
+        <v>0</v>
+      </c>
+      <c r="O27" s="66">
         <f t="shared" si="0"/>
-        <v>-135619.78</v>
-      </c>
-      <c r="P27" s="69">
+        <v>-168789.78</v>
+      </c>
+      <c r="P27" s="67">
         <f t="shared" si="1"/>
-        <v>-139688.78</v>
-      </c>
-      <c r="Q27" s="40">
+        <v>-173853.78</v>
+      </c>
+      <c r="Q27" s="39">
         <f t="shared" si="6"/>
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B28" s="55">
+      <c r="B28" s="54">
         <v>23</v>
       </c>
-      <c r="C28" s="55" t="s">
+      <c r="C28" s="54" t="s">
         <v>73</v>
       </c>
-      <c r="D28" s="55" t="s">
+      <c r="D28" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="E28" s="56"/>
-      <c r="F28" s="61">
+      <c r="E28" s="55"/>
+      <c r="F28" s="59">
         <v>4.66</v>
       </c>
-      <c r="G28" s="62">
-        <v>466000.23</v>
-      </c>
-      <c r="H28" s="63">
-        <v>479980.23</v>
-      </c>
-      <c r="I28" s="64"/>
-      <c r="J28" s="65">
+      <c r="G28" s="60">
+        <v>498620.23</v>
+      </c>
+      <c r="H28" s="61">
+        <f>G28</f>
+        <v>498620.23</v>
+      </c>
+      <c r="I28" s="62"/>
+      <c r="J28" s="63">
         <f t="shared" si="2"/>
-        <v>-13980</v>
-      </c>
-      <c r="K28" s="65">
+        <v>0</v>
+      </c>
+      <c r="K28" s="63">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L28" s="66">
+      <c r="L28" s="64">
         <f t="shared" si="4"/>
         <v>46600</v>
       </c>
-      <c r="M28" s="66">
+      <c r="M28" s="64">
         <f t="shared" si="5"/>
         <v>466000</v>
       </c>
-      <c r="N28" s="67">
-        <v>0</v>
-      </c>
-      <c r="O28" s="68">
+      <c r="N28" s="65">
+        <v>0</v>
+      </c>
+      <c r="O28" s="66">
         <f t="shared" si="0"/>
-        <v>498620.23</v>
-      </c>
-      <c r="P28" s="69">
+        <v>512600.23</v>
+      </c>
+      <c r="P28" s="67">
         <f t="shared" si="1"/>
-        <v>513579.23</v>
-      </c>
-      <c r="Q28" s="40">
+        <v>527978.23</v>
+      </c>
+      <c r="Q28" s="39">
         <f t="shared" si="6"/>
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B29" s="55">
+      <c r="B29" s="54">
         <v>24</v>
       </c>
-      <c r="C29" s="55" t="s">
+      <c r="C29" s="54" t="s">
         <v>74</v>
       </c>
-      <c r="D29" s="55" t="s">
+      <c r="D29" s="54" t="s">
         <v>117</v>
       </c>
-      <c r="E29" s="56"/>
-      <c r="F29" s="61">
+      <c r="E29" s="55"/>
+      <c r="F29" s="59">
         <v>3.21</v>
       </c>
-      <c r="G29" s="62">
-        <v>321000.24</v>
-      </c>
-      <c r="H29" s="63">
+      <c r="G29" s="60">
+        <v>353100.24</v>
+      </c>
+      <c r="H29" s="61">
         <f>G29</f>
-        <v>321000.24</v>
-      </c>
-      <c r="I29" s="64"/>
-      <c r="J29" s="65">
+        <v>353100.24</v>
+      </c>
+      <c r="I29" s="62"/>
+      <c r="J29" s="63">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K29" s="65">
+      <c r="K29" s="63">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L29" s="66">
+      <c r="L29" s="64">
         <f t="shared" si="4"/>
         <v>32099.999999999996</v>
       </c>
-      <c r="M29" s="66">
+      <c r="M29" s="64">
         <f t="shared" si="5"/>
         <v>320999.99999999994</v>
       </c>
-      <c r="N29" s="67">
-        <v>0</v>
-      </c>
-      <c r="O29" s="68">
+      <c r="N29" s="65">
+        <v>0</v>
+      </c>
+      <c r="O29" s="66">
         <f t="shared" si="0"/>
         <v>353100.24</v>
       </c>
-      <c r="P29" s="69">
+      <c r="P29" s="67">
         <f t="shared" si="1"/>
         <v>363693.24</v>
       </c>
-      <c r="Q29" s="40">
+      <c r="Q29" s="39">
         <f t="shared" si="6"/>
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B30" s="55">
+      <c r="B30" s="54">
         <v>25</v>
       </c>
-      <c r="C30" s="55" t="s">
+      <c r="C30" s="54" t="s">
         <v>75</v>
       </c>
-      <c r="D30" s="55" t="s">
+      <c r="D30" s="54" t="s">
         <v>118</v>
       </c>
-      <c r="E30" s="55"/>
-      <c r="F30" s="61">
+      <c r="E30" s="54"/>
+      <c r="F30" s="59">
         <v>4.6900000000000004</v>
       </c>
-      <c r="G30" s="62">
-        <v>469000.25</v>
-      </c>
-      <c r="H30" s="63">
-        <f>G30</f>
-        <v>469000.25</v>
-      </c>
-      <c r="I30" s="64"/>
-      <c r="J30" s="65">
+      <c r="G30" s="60">
+        <v>515900.25</v>
+      </c>
+      <c r="H30" s="61">
+        <v>531377.25</v>
+      </c>
+      <c r="I30" s="62"/>
+      <c r="J30" s="63">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K30" s="65">
+        <v>-15477</v>
+      </c>
+      <c r="K30" s="63">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L30" s="66">
+      <c r="L30" s="64">
         <f t="shared" si="4"/>
         <v>46900.000000000007</v>
       </c>
-      <c r="M30" s="66">
+      <c r="M30" s="64">
         <f t="shared" si="5"/>
         <v>469000.00000000006</v>
       </c>
-      <c r="N30" s="67">
-        <v>0</v>
-      </c>
-      <c r="O30" s="68">
+      <c r="N30" s="65">
+        <v>0</v>
+      </c>
+      <c r="O30" s="66">
         <f t="shared" si="0"/>
-        <v>515900.25</v>
-      </c>
-      <c r="P30" s="69">
+        <v>500423.25</v>
+      </c>
+      <c r="P30" s="67">
         <f t="shared" si="1"/>
-        <v>531377.25</v>
-      </c>
-      <c r="Q30" s="40">
+        <v>515436.25</v>
+      </c>
+      <c r="Q30" s="39">
         <f t="shared" si="6"/>
         <v>0.25000000000000006</v>
       </c>
@@ -4591,311 +4526,307 @@
         <v>142</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B31" s="55">
+      <c r="B31" s="54">
         <v>26</v>
       </c>
-      <c r="C31" s="55" t="s">
+      <c r="C31" s="54" t="s">
         <v>76</v>
       </c>
-      <c r="D31" s="55" t="s">
+      <c r="D31" s="54" t="s">
         <v>119</v>
       </c>
-      <c r="E31" s="55"/>
-      <c r="F31" s="61">
+      <c r="E31" s="54"/>
+      <c r="F31" s="59">
         <v>3.02</v>
       </c>
-      <c r="G31" s="62">
-        <v>293846.26</v>
-      </c>
-      <c r="H31" s="63">
+      <c r="G31" s="60">
+        <v>332200.26</v>
+      </c>
+      <c r="H31" s="61">
         <f>G31</f>
-        <v>293846.26</v>
-      </c>
-      <c r="I31" s="64"/>
-      <c r="J31" s="65">
+        <v>332200.26</v>
+      </c>
+      <c r="I31" s="62"/>
+      <c r="J31" s="63">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K31" s="65">
+      <c r="K31" s="63">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L31" s="66">
+      <c r="L31" s="64">
         <f t="shared" si="4"/>
         <v>30200</v>
       </c>
-      <c r="M31" s="66">
+      <c r="M31" s="64">
         <f t="shared" si="5"/>
         <v>302000</v>
       </c>
-      <c r="N31" s="67">
-        <v>0</v>
-      </c>
-      <c r="O31" s="68">
+      <c r="N31" s="65">
+        <v>31400</v>
+      </c>
+      <c r="O31" s="66">
         <f t="shared" si="0"/>
-        <v>332200.26</v>
-      </c>
-      <c r="P31" s="69">
+        <v>363600.26</v>
+      </c>
+      <c r="P31" s="67">
         <f t="shared" si="1"/>
-        <v>342166.26</v>
-      </c>
-      <c r="Q31" s="114">
+        <v>374508.26</v>
+      </c>
+      <c r="Q31" s="111">
         <f t="shared" si="6"/>
         <v>0.26000000000000006</v>
       </c>
-      <c r="R31" s="119"/>
+      <c r="R31" s="116"/>
       <c r="S31" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:19" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B32" s="55">
+      <c r="B32" s="54">
         <v>27</v>
       </c>
-      <c r="C32" s="55" t="s">
+      <c r="C32" s="54" t="s">
         <v>120</v>
       </c>
-      <c r="D32" s="55" t="s">
+      <c r="D32" s="54" t="s">
         <v>121</v>
       </c>
-      <c r="E32" s="56"/>
-      <c r="F32" s="61">
+      <c r="E32" s="55"/>
+      <c r="F32" s="59">
         <v>0.16</v>
       </c>
-      <c r="G32" s="62">
-        <v>15568.27</v>
-      </c>
-      <c r="H32" s="63">
-        <v>16035</v>
-      </c>
-      <c r="I32" s="64"/>
-      <c r="J32" s="65">
+      <c r="G32" s="60">
+        <v>17133.27</v>
+      </c>
+      <c r="H32" s="61">
+        <f>G32</f>
+        <v>17133.27</v>
+      </c>
+      <c r="I32" s="62"/>
+      <c r="J32" s="63">
         <f>G32-H32</f>
-        <v>-466.72999999999956</v>
-      </c>
-      <c r="K32" s="65">
+        <v>0</v>
+      </c>
+      <c r="K32" s="63">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L32" s="66">
+      <c r="L32" s="64">
         <f t="shared" si="4"/>
         <v>1600</v>
       </c>
-      <c r="M32" s="66">
+      <c r="M32" s="64">
         <f>O$2*F32%</f>
         <v>16000</v>
       </c>
-      <c r="N32" s="67">
-        <v>0</v>
-      </c>
-      <c r="O32" s="68">
+      <c r="N32" s="65">
+        <v>0</v>
+      </c>
+      <c r="O32" s="66">
         <f t="shared" si="0"/>
-        <v>17133.27</v>
-      </c>
-      <c r="P32" s="69">
+        <v>17600.27</v>
+      </c>
+      <c r="P32" s="67">
         <f t="shared" si="1"/>
-        <v>17647.27</v>
-      </c>
-      <c r="Q32" s="40">
+        <v>18128.27</v>
+      </c>
+      <c r="Q32" s="39">
         <f t="shared" si="6"/>
         <v>0.27000000000000007</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B33" s="55"/>
-      <c r="C33" s="55"/>
-      <c r="D33" s="55"/>
-      <c r="E33" s="55"/>
-      <c r="F33" s="61"/>
-      <c r="G33" s="70" t="s">
+      <c r="B33" s="54"/>
+      <c r="C33" s="54"/>
+      <c r="D33" s="54"/>
+      <c r="E33" s="54"/>
+      <c r="F33" s="59"/>
+      <c r="G33" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="H33" s="63" t="str">
+      <c r="H33" s="61" t="str">
         <f t="shared" ref="H33" si="7">G33</f>
         <v>162450.31</v>
       </c>
-      <c r="I33" s="71"/>
-      <c r="J33" s="72" t="e">
+      <c r="I33" s="69"/>
+      <c r="J33" s="70" t="e">
         <f t="shared" ref="J33" si="8">G33-H33</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K33" s="65" t="e">
+      <c r="K33" s="63" t="e">
         <f t="shared" ref="K33" si="9">IF(J33&gt;0,J33*3%,0)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L33" s="66">
+      <c r="L33" s="64">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M33" s="73">
+      <c r="M33" s="71">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N33" s="74">
-        <v>0</v>
-      </c>
-      <c r="O33" s="68" t="e">
+      <c r="N33" s="72">
+        <v>0</v>
+      </c>
+      <c r="O33" s="66" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="P33" s="69" t="e">
+      <c r="P33" s="67" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="Q33" s="40"/>
-    </row>
-    <row r="34" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="75"/>
-      <c r="C34" s="76"/>
-      <c r="D34" s="77"/>
-      <c r="E34" s="77"/>
-      <c r="F34" s="78">
+      <c r="Q33" s="39"/>
+    </row>
+    <row r="34" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="73"/>
+      <c r="C34" s="74"/>
+      <c r="D34" s="75"/>
+      <c r="E34" s="75"/>
+      <c r="F34" s="76">
         <f>SUM(F6:F33)</f>
         <v>99.999999999999972</v>
       </c>
-      <c r="G34" s="46">
+      <c r="G34" s="45">
         <f>SUM(G6:G33)</f>
-        <v>10350546.750000002</v>
-      </c>
-      <c r="H34" s="53">
+        <v>11396016.780000001</v>
+      </c>
+      <c r="H34" s="52">
         <f>SUM(H6:H33)</f>
-        <v>10025643.850000001</v>
-      </c>
-      <c r="I34" s="53">
+        <v>9786183.0700000003</v>
+      </c>
+      <c r="I34" s="52">
         <f t="shared" ref="I34" si="10">SUM(I6:I33)</f>
         <v>0</v>
       </c>
-      <c r="J34" s="53"/>
-      <c r="K34" s="53"/>
-      <c r="L34" s="53">
+      <c r="J34" s="52"/>
+      <c r="K34" s="52"/>
+      <c r="L34" s="52">
         <f>SUM(L6:L33)</f>
         <v>1000000</v>
       </c>
-      <c r="M34" s="53">
+      <c r="M34" s="52">
         <f>SUM(M6:M33)</f>
         <v>10000000</v>
       </c>
-      <c r="N34" s="53">
+      <c r="N34" s="52">
         <f>SUM(N6:N33)</f>
-        <v>5000</v>
-      </c>
-      <c r="O34" s="79">
+        <v>31400</v>
+      </c>
+      <c r="O34" s="77">
         <f>SUM(O6:O32)</f>
-        <v>11357287.780000001</v>
-      </c>
-      <c r="P34" s="79">
+        <v>12705899.779999999</v>
+      </c>
+      <c r="P34" s="77">
         <f>SUM(P6:P32)</f>
-        <v>11698006.780000001</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D35" s="44"/>
-      <c r="E35" s="44"/>
-    </row>
-    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="37" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D37" s="171" t="s">
+        <v>13087077.779999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D35" s="43"/>
+      <c r="E35" s="43"/>
+    </row>
+    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D37" s="156" t="s">
         <v>148</v>
       </c>
-      <c r="E37" s="171"/>
-      <c r="F37" s="171"/>
-      <c r="G37" s="171"/>
-      <c r="H37" s="171"/>
-      <c r="I37" s="171"/>
-      <c r="J37" s="171"/>
-      <c r="K37" s="171"/>
-      <c r="L37" s="171"/>
-      <c r="M37" s="171"/>
-      <c r="N37" s="171"/>
-      <c r="O37" s="171"/>
-    </row>
-    <row r="38" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D38" s="171"/>
-      <c r="E38" s="171"/>
-      <c r="F38" s="171"/>
-      <c r="G38" s="171"/>
-      <c r="H38" s="171"/>
-      <c r="I38" s="171"/>
-      <c r="J38" s="171"/>
-      <c r="K38" s="171"/>
-      <c r="L38" s="171"/>
-      <c r="M38" s="171"/>
-      <c r="N38" s="171"/>
-      <c r="O38" s="171"/>
-    </row>
-    <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D39" s="171"/>
-      <c r="E39" s="171"/>
-      <c r="F39" s="171"/>
-      <c r="G39" s="171"/>
-      <c r="H39" s="171"/>
-      <c r="I39" s="171"/>
-      <c r="J39" s="171"/>
-      <c r="K39" s="171"/>
-      <c r="L39" s="171"/>
-      <c r="M39" s="171"/>
-      <c r="N39" s="171"/>
-      <c r="O39" s="171"/>
-    </row>
-    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D40" s="171"/>
-      <c r="E40" s="171"/>
-      <c r="F40" s="171"/>
-      <c r="G40" s="171"/>
-      <c r="H40" s="171"/>
-      <c r="I40" s="171"/>
-      <c r="J40" s="171"/>
-      <c r="K40" s="171"/>
-      <c r="L40" s="171"/>
-      <c r="M40" s="171"/>
-      <c r="N40" s="171"/>
-      <c r="O40" s="171"/>
-    </row>
-    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D41" s="171"/>
-      <c r="E41" s="171"/>
-      <c r="F41" s="171"/>
-      <c r="G41" s="171"/>
-      <c r="H41" s="171"/>
-      <c r="I41" s="171"/>
-      <c r="J41" s="171"/>
-      <c r="K41" s="171"/>
-      <c r="L41" s="171"/>
-      <c r="M41" s="171"/>
-      <c r="N41" s="171"/>
-      <c r="O41" s="171"/>
-    </row>
-    <row r="42" spans="1:17" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D42" s="171"/>
-      <c r="E42" s="171"/>
-      <c r="F42" s="171"/>
-      <c r="G42" s="171"/>
-      <c r="H42" s="171"/>
-      <c r="I42" s="171"/>
-      <c r="J42" s="171"/>
-      <c r="K42" s="171"/>
-      <c r="L42" s="171"/>
-      <c r="M42" s="171"/>
-      <c r="N42" s="171"/>
-      <c r="O42" s="171"/>
+      <c r="E37" s="156"/>
+      <c r="F37" s="156"/>
+      <c r="G37" s="156"/>
+      <c r="H37" s="156"/>
+      <c r="I37" s="156"/>
+      <c r="J37" s="156"/>
+      <c r="K37" s="156"/>
+      <c r="L37" s="156"/>
+      <c r="M37" s="156"/>
+      <c r="N37" s="156"/>
+      <c r="O37" s="156"/>
+    </row>
+    <row r="38" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D38" s="156"/>
+      <c r="E38" s="156"/>
+      <c r="F38" s="156"/>
+      <c r="G38" s="156"/>
+      <c r="H38" s="156"/>
+      <c r="I38" s="156"/>
+      <c r="J38" s="156"/>
+      <c r="K38" s="156"/>
+      <c r="L38" s="156"/>
+      <c r="M38" s="156"/>
+      <c r="N38" s="156"/>
+      <c r="O38" s="156"/>
+    </row>
+    <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D39" s="156"/>
+      <c r="E39" s="156"/>
+      <c r="F39" s="156"/>
+      <c r="G39" s="156"/>
+      <c r="H39" s="156"/>
+      <c r="I39" s="156"/>
+      <c r="J39" s="156"/>
+      <c r="K39" s="156"/>
+      <c r="L39" s="156"/>
+      <c r="M39" s="156"/>
+      <c r="N39" s="156"/>
+      <c r="O39" s="156"/>
+    </row>
+    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D40" s="156"/>
+      <c r="E40" s="156"/>
+      <c r="F40" s="156"/>
+      <c r="G40" s="156"/>
+      <c r="H40" s="156"/>
+      <c r="I40" s="156"/>
+      <c r="J40" s="156"/>
+      <c r="K40" s="156"/>
+      <c r="L40" s="156"/>
+      <c r="M40" s="156"/>
+      <c r="N40" s="156"/>
+      <c r="O40" s="156"/>
+    </row>
+    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D41" s="156"/>
+      <c r="E41" s="156"/>
+      <c r="F41" s="156"/>
+      <c r="G41" s="156"/>
+      <c r="H41" s="156"/>
+      <c r="I41" s="156"/>
+      <c r="J41" s="156"/>
+      <c r="K41" s="156"/>
+      <c r="L41" s="156"/>
+      <c r="M41" s="156"/>
+      <c r="N41" s="156"/>
+      <c r="O41" s="156"/>
+    </row>
+    <row r="42" spans="1:17" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D42" s="156"/>
+      <c r="E42" s="156"/>
+      <c r="F42" s="156"/>
+      <c r="G42" s="156"/>
+      <c r="H42" s="156"/>
+      <c r="I42" s="156"/>
+      <c r="J42" s="156"/>
+      <c r="K42" s="156"/>
+      <c r="L42" s="156"/>
+      <c r="M42" s="156"/>
+      <c r="N42" s="156"/>
+      <c r="O42" s="156"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="F4:F5"/>
     <mergeCell ref="B1:K3"/>
     <mergeCell ref="P4:P5"/>
     <mergeCell ref="D37:O42"/>
@@ -4908,6 +4839,11 @@
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="N4:N5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="F4:F5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>

--- a/2026/COLOMBRES/ENERO/Enero COLOMBRES 360.xlsx
+++ b/2026/COLOMBRES/ENERO/Enero COLOMBRES 360.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\2026\COLOMBRES\ENERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2506757-7C40-4971-8463-C65C99731065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27712371-77F0-4A55-B386-3C097BB489AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
     <sheet name="PRORRATEO" sheetId="2" r:id="rId2"/>
+    <sheet name="ANOTACIONES" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$43</definedName>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="189">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -594,6 +595,9 @@
   </si>
   <si>
     <t>QUEDO PENDIENTE PARA FEBR3R0 PASAR UN EDESUR DE EN3RO</t>
+  </si>
+  <si>
+    <t>Los depositos sin identificar del 15/01 son de sergio</t>
   </si>
 </sst>
 </file>
@@ -796,7 +800,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -869,6 +873,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="30">
     <border>
@@ -1227,7 +1237,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="193">
+  <cellXfs count="202">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1387,7 +1397,6 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="24" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1454,6 +1463,48 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="20" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1469,46 +1520,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1523,48 +1574,18 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="20" fillId="13" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="20" fillId="13" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="13" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="13" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="13" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="13" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1957,68 +1978,68 @@
       <c r="D3" s="109"/>
     </row>
     <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="173" t="s">
+      <c r="A4" s="160" t="s">
         <v>124</v>
       </c>
-      <c r="B4" s="173"/>
+      <c r="B4" s="160"/>
       <c r="C4" s="110"/>
       <c r="D4" s="110"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="173"/>
-      <c r="B5" s="173"/>
+      <c r="A5" s="160"/>
+      <c r="B5" s="160"/>
       <c r="C5" s="110"/>
       <c r="D5" s="110"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="173"/>
-      <c r="B6" s="173"/>
+      <c r="A6" s="160"/>
+      <c r="B6" s="160"/>
       <c r="C6" s="110"/>
       <c r="D6" s="110"/>
     </row>
     <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="173"/>
-      <c r="B7" s="173"/>
+      <c r="A7" s="160"/>
+      <c r="B7" s="160"/>
       <c r="C7" s="110"/>
       <c r="D7" s="110"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="172" t="s">
+      <c r="B9" s="157" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="172"/>
+      <c r="B10" s="157"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="172"/>
+      <c r="B11" s="157"/>
     </row>
     <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="174" t="s">
+      <c r="A14" s="161" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="174"/>
-      <c r="C14" s="174"/>
-      <c r="D14" s="174"/>
+      <c r="B14" s="161"/>
+      <c r="C14" s="161"/>
+      <c r="D14" s="161"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="174"/>
-      <c r="B15" s="174"/>
-      <c r="C15" s="174"/>
-      <c r="D15" s="174"/>
+      <c r="A15" s="161"/>
+      <c r="B15" s="161"/>
+      <c r="C15" s="161"/>
+      <c r="D15" s="161"/>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="174"/>
-      <c r="B16" s="174"/>
-      <c r="C16" s="174"/>
-      <c r="D16" s="174"/>
+      <c r="A16" s="161"/>
+      <c r="B16" s="161"/>
+      <c r="C16" s="161"/>
+      <c r="D16" s="161"/>
     </row>
     <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="174"/>
-      <c r="B17" s="174"/>
-      <c r="C17" s="174"/>
-      <c r="D17" s="174"/>
+      <c r="A17" s="161"/>
+      <c r="B17" s="161"/>
+      <c r="C17" s="161"/>
+      <c r="D17" s="161"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2048,7 +2069,7 @@
       <c r="B23" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="C23" s="138">
+      <c r="C23" s="137">
         <v>1774070.07</v>
       </c>
       <c r="D23" s="80"/>
@@ -2058,7 +2079,7 @@
         <v>84</v>
       </c>
       <c r="B24" s="5"/>
-      <c r="C24" s="138">
+      <c r="C24" s="137">
         <f>-732912.7</f>
         <v>-732912.7</v>
       </c>
@@ -2069,7 +2090,7 @@
         <v>83</v>
       </c>
       <c r="B25" s="5"/>
-      <c r="C25" s="138">
+      <c r="C25" s="137">
         <v>0.63</v>
       </c>
       <c r="D25" s="80"/>
@@ -2078,7 +2099,7 @@
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
-      <c r="C26" s="138"/>
+      <c r="C26" s="137"/>
       <c r="D26" s="80"/>
       <c r="G26" s="14"/>
     </row>
@@ -2092,10 +2113,10 @@
         <v>1041158.0000000001</v>
       </c>
       <c r="D27" s="81"/>
-      <c r="F27" s="170" t="s">
+      <c r="F27" s="155" t="s">
         <v>145</v>
       </c>
-      <c r="G27" s="171"/>
+      <c r="G27" s="156"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
@@ -2104,7 +2125,7 @@
       <c r="B28" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="C28" s="138">
+      <c r="C28" s="137">
         <v>1301013.8899999999</v>
       </c>
       <c r="D28" s="113"/>
@@ -2114,7 +2135,7 @@
         <v>81</v>
       </c>
       <c r="B29" s="5"/>
-      <c r="C29" s="138">
+      <c r="C29" s="137">
         <v>-282970.53000000003</v>
       </c>
       <c r="D29" s="113"/>
@@ -2124,7 +2145,7 @@
         <v>83</v>
       </c>
       <c r="B30" s="5"/>
-      <c r="C30" s="138">
+      <c r="C30" s="137">
         <v>0.64</v>
       </c>
       <c r="D30" s="113"/>
@@ -2132,7 +2153,7 @@
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
-      <c r="C31" s="139"/>
+      <c r="C31" s="138"/>
       <c r="D31" s="113"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -2173,10 +2194,10 @@
         <v>39</v>
       </c>
       <c r="B35" s="5"/>
-      <c r="C35" s="138">
+      <c r="C35" s="137">
         <v>70000</v>
       </c>
-      <c r="D35" s="125" t="s">
+      <c r="D35" s="124" t="s">
         <v>163</v>
       </c>
       <c r="G35" s="14"/>
@@ -2188,10 +2209,10 @@
       <c r="B36" s="107" t="s">
         <v>156</v>
       </c>
-      <c r="C36" s="138">
+      <c r="C36" s="137">
         <v>211800</v>
       </c>
-      <c r="D36" s="125" t="s">
+      <c r="D36" s="124" t="s">
         <v>178</v>
       </c>
       <c r="G36" s="14"/>
@@ -2216,24 +2237,24 @@
       <c r="D38" s="57"/>
     </row>
     <row r="39" spans="1:7" s="33" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="166" t="s">
+      <c r="A39" s="158" t="s">
         <v>127</v>
       </c>
-      <c r="B39" s="167"/>
-      <c r="C39" s="140" t="s">
+      <c r="B39" s="159"/>
+      <c r="C39" s="139" t="s">
         <v>180</v>
       </c>
-      <c r="D39" s="124"/>
+      <c r="D39" s="123"/>
     </row>
     <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="166" t="s">
+      <c r="A40" s="158" t="s">
         <v>128</v>
       </c>
-      <c r="B40" s="167"/>
-      <c r="C40" s="147">
+      <c r="B40" s="159"/>
+      <c r="C40" s="146">
         <v>4203</v>
       </c>
-      <c r="D40" s="124" t="s">
+      <c r="D40" s="123" t="s">
         <v>179</v>
       </c>
     </row>
@@ -2252,7 +2273,7 @@
       <c r="A42" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="B42" s="148"/>
+      <c r="B42" s="147"/>
       <c r="C42" s="31"/>
       <c r="D42" s="85"/>
     </row>
@@ -2263,10 +2284,10 @@
       <c r="B43" s="80" t="s">
         <v>160</v>
       </c>
-      <c r="C43" s="141">
+      <c r="C43" s="140">
         <v>2082831.51</v>
       </c>
-      <c r="D43" s="124" t="s">
+      <c r="D43" s="123" t="s">
         <v>169</v>
       </c>
       <c r="F43" s="116"/>
@@ -2278,10 +2299,10 @@
       <c r="B44" s="80" t="s">
         <v>160</v>
       </c>
-      <c r="C44" s="149">
+      <c r="C44" s="148">
         <v>24115.91</v>
       </c>
-      <c r="D44" s="124" t="s">
+      <c r="D44" s="123" t="s">
         <v>172</v>
       </c>
     </row>
@@ -2292,10 +2313,10 @@
       <c r="B45" s="80" t="s">
         <v>160</v>
       </c>
-      <c r="C45" s="149">
+      <c r="C45" s="148">
         <v>217043.12</v>
       </c>
-      <c r="D45" s="124" t="str">
+      <c r="D45" s="123" t="str">
         <f>D44</f>
         <v>Debito 13/01</v>
       </c>
@@ -2307,10 +2328,10 @@
       <c r="B46" s="80" t="s">
         <v>160</v>
       </c>
-      <c r="C46" s="149">
+      <c r="C46" s="148">
         <v>397626.72</v>
       </c>
-      <c r="D46" s="122" t="str">
+      <c r="D46" s="121" t="str">
         <f>D45</f>
         <v>Debito 13/01</v>
       </c>
@@ -2319,7 +2340,7 @@
       <c r="A47" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="B47" s="148"/>
+      <c r="B47" s="147"/>
       <c r="C47" s="32"/>
       <c r="D47" s="84">
         <f>SUM(C43:C46)</f>
@@ -2330,7 +2351,7 @@
       <c r="A48" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="B48" s="148"/>
+      <c r="B48" s="147"/>
       <c r="C48" s="31"/>
       <c r="D48" s="85"/>
     </row>
@@ -2339,10 +2360,10 @@
         <v>136</v>
       </c>
       <c r="B49" s="80"/>
-      <c r="C49" s="149">
+      <c r="C49" s="148">
         <v>569002.89</v>
       </c>
-      <c r="D49" s="121" t="s">
+      <c r="D49" s="120" t="s">
         <v>167</v>
       </c>
     </row>
@@ -2351,10 +2372,10 @@
         <v>125</v>
       </c>
       <c r="B50" s="80"/>
-      <c r="C50" s="149">
+      <c r="C50" s="148">
         <v>20769.7</v>
       </c>
-      <c r="D50" s="121" t="s">
+      <c r="D50" s="120" t="s">
         <v>167</v>
       </c>
       <c r="F50" t="s">
@@ -2366,46 +2387,46 @@
         <v>138</v>
       </c>
       <c r="B51" s="80"/>
-      <c r="C51" s="149">
+      <c r="C51" s="148">
         <v>864000.26</v>
       </c>
-      <c r="D51" s="121" t="s">
+      <c r="D51" s="120" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="168" t="s">
+      <c r="A52" s="167" t="s">
         <v>157</v>
       </c>
-      <c r="B52" s="169"/>
-      <c r="C52" s="149">
+      <c r="B52" s="168"/>
+      <c r="C52" s="148">
         <v>204149</v>
       </c>
-      <c r="D52" s="121" t="s">
+      <c r="D52" s="120" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="164" t="s">
+      <c r="A53" s="165" t="s">
         <v>170</v>
       </c>
-      <c r="B53" s="165"/>
-      <c r="C53" s="149">
+      <c r="B53" s="166"/>
+      <c r="C53" s="148">
         <v>100000</v>
       </c>
-      <c r="D53" s="123" t="s">
+      <c r="D53" s="122" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="166" t="s">
+      <c r="A54" s="158" t="s">
         <v>153</v>
       </c>
-      <c r="B54" s="167"/>
-      <c r="C54" s="149">
+      <c r="B54" s="159"/>
+      <c r="C54" s="148">
         <v>35200</v>
       </c>
-      <c r="D54" s="123" t="s">
+      <c r="D54" s="122" t="s">
         <v>175</v>
       </c>
     </row>
@@ -2429,11 +2450,11 @@
       <c r="D56" s="87"/>
     </row>
     <row r="57" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="150" t="s">
+      <c r="A57" s="149" t="s">
         <v>164</v>
       </c>
-      <c r="B57" s="151"/>
-      <c r="C57" s="149">
+      <c r="B57" s="150"/>
+      <c r="C57" s="148">
         <v>11850</v>
       </c>
       <c r="D57" s="118" t="s">
@@ -2441,11 +2462,11 @@
       </c>
     </row>
     <row r="58" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="150" t="s">
+      <c r="A58" s="149" t="s">
         <v>182</v>
       </c>
-      <c r="B58" s="151"/>
-      <c r="C58" s="149">
+      <c r="B58" s="150"/>
+      <c r="C58" s="148">
         <v>5400</v>
       </c>
       <c r="D58" s="118" t="s">
@@ -2453,11 +2474,11 @@
       </c>
     </row>
     <row r="59" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="152" t="s">
+      <c r="A59" s="151" t="s">
         <v>165</v>
       </c>
-      <c r="B59" s="153"/>
-      <c r="C59" s="149">
+      <c r="B59" s="152"/>
+      <c r="C59" s="148">
         <v>184942.62</v>
       </c>
       <c r="D59" s="118" t="s">
@@ -2465,11 +2486,11 @@
       </c>
     </row>
     <row r="60" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="166" t="s">
+      <c r="A60" s="158" t="s">
         <v>177</v>
       </c>
-      <c r="B60" s="167"/>
-      <c r="C60" s="149">
+      <c r="B60" s="159"/>
+      <c r="C60" s="148">
         <v>250000</v>
       </c>
       <c r="D60" s="118" t="s">
@@ -2477,11 +2498,11 @@
       </c>
     </row>
     <row r="61" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="152" t="s">
+      <c r="A61" s="151" t="s">
         <v>173</v>
       </c>
-      <c r="B61" s="151"/>
-      <c r="C61" s="149">
+      <c r="B61" s="150"/>
+      <c r="C61" s="148">
         <v>96111.67</v>
       </c>
       <c r="D61" s="118" t="s">
@@ -2489,64 +2510,64 @@
       </c>
     </row>
     <row r="62" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="166" t="s">
+      <c r="A62" s="158" t="s">
         <v>168</v>
       </c>
-      <c r="B62" s="167"/>
-      <c r="C62" s="149">
+      <c r="B62" s="159"/>
+      <c r="C62" s="148">
         <v>750000</v>
       </c>
-      <c r="D62" s="121" t="s">
+      <c r="D62" s="120" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="145" t="s">
+      <c r="A63" s="144" t="s">
         <v>184</v>
       </c>
-      <c r="B63" s="146"/>
-      <c r="C63" s="149">
+      <c r="B63" s="145"/>
+      <c r="C63" s="148">
         <v>128083.59</v>
       </c>
-      <c r="D63" s="144" t="s">
+      <c r="D63" s="143" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="166" t="s">
+      <c r="A64" s="158" t="s">
         <v>183</v>
       </c>
-      <c r="B64" s="167"/>
-      <c r="C64" s="149">
+      <c r="B64" s="159"/>
+      <c r="C64" s="148">
         <v>180000</v>
       </c>
-      <c r="D64" s="144" t="s">
+      <c r="D64" s="143" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="166" t="s">
+      <c r="A65" s="158" t="s">
         <v>161</v>
       </c>
-      <c r="B65" s="167"/>
-      <c r="C65" s="149">
+      <c r="B65" s="159"/>
+      <c r="C65" s="148">
         <v>35000</v>
       </c>
-      <c r="D65" s="123" t="s">
+      <c r="D65" s="122" t="s">
         <v>162</v>
       </c>
       <c r="E65" s="39"/>
       <c r="F65" s="39"/>
     </row>
     <row r="66" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="164" t="s">
+      <c r="A66" s="165" t="s">
         <v>158</v>
       </c>
-      <c r="B66" s="165"/>
-      <c r="C66" s="141">
-        <v>0</v>
-      </c>
-      <c r="D66" s="123"/>
+      <c r="B66" s="166"/>
+      <c r="C66" s="140">
+        <v>0</v>
+      </c>
+      <c r="D66" s="122"/>
     </row>
     <row r="67" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="25" t="s">
@@ -2563,7 +2584,7 @@
       <c r="A68" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="B68" s="154"/>
+      <c r="B68" s="153"/>
       <c r="C68" s="19"/>
       <c r="D68" s="87"/>
     </row>
@@ -2572,7 +2593,7 @@
         <v>137</v>
       </c>
       <c r="B69" s="80"/>
-      <c r="C69" s="149">
+      <c r="C69" s="148">
         <v>65343</v>
       </c>
       <c r="D69" s="91"/>
@@ -2582,7 +2603,7 @@
         <v>126</v>
       </c>
       <c r="B70" s="80"/>
-      <c r="C70" s="149">
+      <c r="C70" s="148">
         <f>1270.8+130081.56+168.5+1080+1392+150+600+950+1062</f>
         <v>136754.85999999999</v>
       </c>
@@ -2606,11 +2627,11 @@
       <c r="D72" s="93"/>
     </row>
     <row r="73" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="161" t="s">
+      <c r="A73" s="162" t="s">
         <v>144</v>
       </c>
-      <c r="B73" s="162"/>
-      <c r="C73" s="163"/>
+      <c r="B73" s="163"/>
+      <c r="C73" s="164"/>
       <c r="D73" s="94">
         <f>10000000-8703429.85</f>
         <v>1296570.1500000004</v>
@@ -2653,14 +2674,14 @@
       <c r="D78" s="100"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="159"/>
-      <c r="B79" s="160"/>
+      <c r="A79" s="172"/>
+      <c r="B79" s="173"/>
       <c r="C79" s="88"/>
       <c r="D79" s="86"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="159"/>
-      <c r="B80" s="160"/>
+      <c r="A80" s="172"/>
+      <c r="B80" s="173"/>
       <c r="C80" s="88"/>
       <c r="D80" s="86"/>
     </row>
@@ -2687,7 +2708,7 @@
       </c>
       <c r="B85" s="20"/>
       <c r="C85" s="21"/>
-      <c r="D85" s="126">
+      <c r="D85" s="125">
         <v>1000000</v>
       </c>
     </row>
@@ -2742,24 +2763,24 @@
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" s="158" t="s">
+      <c r="A95" s="171" t="s">
         <v>159</v>
       </c>
-      <c r="B95" s="158"/>
-      <c r="C95" s="158"/>
-      <c r="D95" s="158"/>
+      <c r="B95" s="171"/>
+      <c r="C95" s="171"/>
+      <c r="D95" s="171"/>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A96" s="158"/>
-      <c r="B96" s="158"/>
-      <c r="C96" s="158"/>
-      <c r="D96" s="158"/>
+      <c r="A96" s="171"/>
+      <c r="B96" s="171"/>
+      <c r="C96" s="171"/>
+      <c r="D96" s="171"/>
     </row>
     <row r="97" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="158"/>
-      <c r="B97" s="158"/>
-      <c r="C97" s="158"/>
-      <c r="D97" s="158"/>
+      <c r="A97" s="171"/>
+      <c r="B97" s="171"/>
+      <c r="C97" s="171"/>
+      <c r="D97" s="171"/>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="15" t="s">
@@ -2797,13 +2818,13 @@
       <c r="A103" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="B103" s="120"/>
+      <c r="B103" s="119"/>
     </row>
     <row r="104" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="B104" s="120">
+      <c r="B104" s="119">
         <v>-31400</v>
       </c>
     </row>
@@ -2811,7 +2832,7 @@
       <c r="A105" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="B105" s="120">
+      <c r="B105" s="119">
         <f>-B90</f>
         <v>-8703429.8499999996</v>
       </c>
@@ -2839,14 +2860,14 @@
       <c r="C108" s="39"/>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A110" s="157" t="s">
+      <c r="A110" s="170" t="s">
         <v>78</v>
       </c>
-      <c r="B110" s="157"/>
+      <c r="B110" s="170"/>
     </row>
     <row r="111" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="157"/>
-      <c r="B111" s="157"/>
+      <c r="A111" s="170"/>
+      <c r="B111" s="170"/>
     </row>
     <row r="112" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="101" t="s">
@@ -2877,37 +2898,36 @@
       <c r="L115" s="8"/>
     </row>
     <row r="116" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="156"/>
-      <c r="B116" s="156"/>
-      <c r="C116" s="156"/>
-      <c r="D116" s="156"/>
+      <c r="A116" s="169"/>
+      <c r="B116" s="169"/>
+      <c r="C116" s="169"/>
+      <c r="D116" s="169"/>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A117" s="156"/>
-      <c r="B117" s="156"/>
-      <c r="C117" s="156"/>
-      <c r="D117" s="156"/>
+      <c r="A117" s="169"/>
+      <c r="B117" s="169"/>
+      <c r="C117" s="169"/>
+      <c r="D117" s="169"/>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A118" s="156"/>
-      <c r="B118" s="156"/>
-      <c r="C118" s="156"/>
-      <c r="D118" s="156"/>
+      <c r="A118" s="169"/>
+      <c r="B118" s="169"/>
+      <c r="C118" s="169"/>
+      <c r="D118" s="169"/>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A119" s="156"/>
-      <c r="B119" s="156"/>
-      <c r="C119" s="156"/>
-      <c r="D119" s="156"/>
+      <c r="A119" s="169"/>
+      <c r="B119" s="169"/>
+      <c r="C119" s="169"/>
+      <c r="D119" s="169"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A4:B7"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A14:D17"/>
+    <mergeCell ref="A116:D119"/>
+    <mergeCell ref="A110:B111"/>
+    <mergeCell ref="A95:D97"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="A79:B79"/>
     <mergeCell ref="A73:C73"/>
     <mergeCell ref="A66:B66"/>
     <mergeCell ref="A65:B65"/>
@@ -2917,11 +2937,12 @@
     <mergeCell ref="A62:B62"/>
     <mergeCell ref="A54:B54"/>
     <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A116:D119"/>
-    <mergeCell ref="A110:B111"/>
-    <mergeCell ref="A95:D97"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A4:B7"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A14:D17"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2957,18 +2978,18 @@
   <sheetData>
     <row r="1" spans="1:19" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
-      <c r="B1" s="181" t="s">
+      <c r="B1" s="174" t="s">
         <v>147</v>
       </c>
-      <c r="C1" s="181"/>
-      <c r="D1" s="181"/>
-      <c r="E1" s="181"/>
-      <c r="F1" s="181"/>
-      <c r="G1" s="181"/>
-      <c r="H1" s="181"/>
-      <c r="I1" s="181"/>
-      <c r="J1" s="181"/>
-      <c r="K1" s="181"/>
+      <c r="C1" s="174"/>
+      <c r="D1" s="174"/>
+      <c r="E1" s="174"/>
+      <c r="F1" s="174"/>
+      <c r="G1" s="174"/>
+      <c r="H1" s="174"/>
+      <c r="I1" s="174"/>
+      <c r="J1" s="174"/>
+      <c r="K1" s="174"/>
       <c r="L1" s="6"/>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
@@ -2977,22 +2998,22 @@
     </row>
     <row r="2" spans="1:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
-      <c r="B2" s="181"/>
-      <c r="C2" s="181"/>
-      <c r="D2" s="181"/>
-      <c r="E2" s="181"/>
-      <c r="F2" s="181"/>
-      <c r="G2" s="181"/>
-      <c r="H2" s="181"/>
-      <c r="I2" s="181"/>
-      <c r="J2" s="181"/>
-      <c r="K2" s="181"/>
+      <c r="B2" s="174"/>
+      <c r="C2" s="174"/>
+      <c r="D2" s="174"/>
+      <c r="E2" s="174"/>
+      <c r="F2" s="174"/>
+      <c r="G2" s="174"/>
+      <c r="H2" s="174"/>
+      <c r="I2" s="174"/>
+      <c r="J2" s="174"/>
+      <c r="K2" s="174"/>
       <c r="L2" s="7" t="s">
         <v>4</v>
       </c>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
-      <c r="O2" s="142">
+      <c r="O2" s="141">
         <v>10000000</v>
       </c>
       <c r="P2" s="46"/>
@@ -3000,97 +3021,97 @@
     </row>
     <row r="3" spans="1:19" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
-      <c r="B3" s="182"/>
-      <c r="C3" s="182"/>
-      <c r="D3" s="182"/>
-      <c r="E3" s="182"/>
-      <c r="F3" s="182"/>
-      <c r="G3" s="182"/>
-      <c r="H3" s="182"/>
-      <c r="I3" s="182"/>
-      <c r="J3" s="182"/>
-      <c r="K3" s="182"/>
+      <c r="B3" s="175"/>
+      <c r="C3" s="175"/>
+      <c r="D3" s="175"/>
+      <c r="E3" s="175"/>
+      <c r="F3" s="175"/>
+      <c r="G3" s="175"/>
+      <c r="H3" s="175"/>
+      <c r="I3" s="175"/>
+      <c r="J3" s="175"/>
+      <c r="K3" s="175"/>
       <c r="L3" s="7" t="s">
         <v>93</v>
       </c>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
-      <c r="O3" s="143">
+      <c r="O3" s="142">
         <v>1000000</v>
       </c>
       <c r="P3" s="50"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="175" t="s">
+      <c r="A4" s="188" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="177" t="s">
+      <c r="B4" s="190" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="179" t="s">
+      <c r="C4" s="178" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="179" t="s">
+      <c r="D4" s="178" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="179" t="s">
+      <c r="E4" s="178" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="179" t="s">
+      <c r="F4" s="178" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="179" t="s">
+      <c r="G4" s="178" t="s">
         <v>89</v>
       </c>
-      <c r="H4" s="179" t="s">
+      <c r="H4" s="178" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="179" t="s">
+      <c r="I4" s="178" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="188" t="s">
+      <c r="J4" s="183" t="s">
         <v>50</v>
       </c>
-      <c r="K4" s="186" t="s">
+      <c r="K4" s="180" t="s">
         <v>47</v>
       </c>
-      <c r="L4" s="186" t="s">
+      <c r="L4" s="180" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="186" t="s">
+      <c r="M4" s="180" t="s">
         <v>46</v>
       </c>
-      <c r="N4" s="191" t="s">
+      <c r="N4" s="186" t="s">
         <v>87</v>
       </c>
       <c r="O4" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="P4" s="183" t="s">
+      <c r="P4" s="176" t="s">
         <v>85</v>
       </c>
       <c r="S4" s="39"/>
     </row>
     <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="176"/>
-      <c r="B5" s="178"/>
-      <c r="C5" s="180"/>
-      <c r="D5" s="180"/>
-      <c r="E5" s="185"/>
-      <c r="F5" s="180"/>
-      <c r="G5" s="180"/>
-      <c r="H5" s="180"/>
-      <c r="I5" s="185"/>
-      <c r="J5" s="189"/>
-      <c r="K5" s="187"/>
-      <c r="L5" s="190"/>
-      <c r="M5" s="187"/>
-      <c r="N5" s="192"/>
+      <c r="A5" s="189"/>
+      <c r="B5" s="191"/>
+      <c r="C5" s="182"/>
+      <c r="D5" s="182"/>
+      <c r="E5" s="179"/>
+      <c r="F5" s="182"/>
+      <c r="G5" s="182"/>
+      <c r="H5" s="182"/>
+      <c r="I5" s="179"/>
+      <c r="J5" s="184"/>
+      <c r="K5" s="181"/>
+      <c r="L5" s="185"/>
+      <c r="M5" s="181"/>
+      <c r="N5" s="187"/>
       <c r="O5" s="51" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 16/02</v>
       </c>
-      <c r="P5" s="184"/>
+      <c r="P5" s="177"/>
     </row>
     <row r="6" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
@@ -3212,48 +3233,48 @@
       <c r="A8" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="127">
+      <c r="B8" s="126">
         <v>3</v>
       </c>
-      <c r="C8" s="127" t="s">
+      <c r="C8" s="126" t="s">
         <v>53</v>
       </c>
-      <c r="D8" s="128" t="s">
+      <c r="D8" s="127" t="s">
         <v>146</v>
       </c>
-      <c r="E8" s="129"/>
-      <c r="F8" s="130">
+      <c r="E8" s="128"/>
+      <c r="F8" s="129">
         <v>4.55</v>
       </c>
-      <c r="G8" s="131">
+      <c r="G8" s="130">
         <v>500500.03</v>
       </c>
-      <c r="H8" s="131"/>
-      <c r="I8" s="132"/>
-      <c r="J8" s="133">
+      <c r="H8" s="130"/>
+      <c r="I8" s="131"/>
+      <c r="J8" s="132">
         <f t="shared" si="2"/>
         <v>500500.03</v>
       </c>
-      <c r="K8" s="133">
+      <c r="K8" s="132">
         <f t="shared" si="3"/>
         <v>14764.750885000001</v>
       </c>
-      <c r="L8" s="134">
+      <c r="L8" s="133">
         <f t="shared" si="4"/>
         <v>45500</v>
       </c>
-      <c r="M8" s="134">
+      <c r="M8" s="133">
         <f t="shared" si="5"/>
         <v>455000</v>
       </c>
-      <c r="N8" s="135">
-        <v>0</v>
-      </c>
-      <c r="O8" s="136">
+      <c r="N8" s="134">
+        <v>0</v>
+      </c>
+      <c r="O8" s="135">
         <f t="shared" si="0"/>
         <v>1015765.03</v>
       </c>
-      <c r="P8" s="137">
+      <c r="P8" s="136">
         <f t="shared" si="1"/>
         <v>1046238.03</v>
       </c>
@@ -3441,48 +3462,48 @@
       <c r="A12" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="54">
+      <c r="B12" s="192">
         <v>7</v>
       </c>
-      <c r="C12" s="119" t="s">
+      <c r="C12" s="192" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="119" t="s">
+      <c r="D12" s="192" t="s">
         <v>100</v>
       </c>
-      <c r="E12" s="54"/>
-      <c r="F12" s="59">
+      <c r="E12" s="192"/>
+      <c r="F12" s="193">
         <v>4.55</v>
       </c>
-      <c r="G12" s="60">
+      <c r="G12" s="194">
         <v>496500.07</v>
       </c>
-      <c r="H12" s="61"/>
-      <c r="I12" s="62"/>
-      <c r="J12" s="63">
+      <c r="H12" s="194"/>
+      <c r="I12" s="195"/>
+      <c r="J12" s="196">
         <f t="shared" si="2"/>
         <v>496500.07</v>
       </c>
-      <c r="K12" s="63">
+      <c r="K12" s="196">
         <f t="shared" si="3"/>
         <v>14646.752065000001</v>
       </c>
-      <c r="L12" s="64">
+      <c r="L12" s="197">
         <f t="shared" si="4"/>
         <v>45500</v>
       </c>
-      <c r="M12" s="64">
+      <c r="M12" s="197">
         <f t="shared" si="5"/>
         <v>455000</v>
       </c>
-      <c r="N12" s="65">
-        <v>0</v>
-      </c>
-      <c r="O12" s="66">
+      <c r="N12" s="198">
+        <v>0</v>
+      </c>
+      <c r="O12" s="199">
         <f t="shared" si="0"/>
         <v>1011647.07</v>
       </c>
-      <c r="P12" s="67">
+      <c r="P12" s="200">
         <f t="shared" si="1"/>
         <v>1041996.07</v>
       </c>
@@ -3569,7 +3590,7 @@
       <c r="G14" s="60">
         <v>487200.09</v>
       </c>
-      <c r="H14" s="155">
+      <c r="H14" s="154">
         <v>490000</v>
       </c>
       <c r="I14" s="62"/>
@@ -4740,93 +4761,98 @@
     </row>
     <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="37" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D37" s="156" t="s">
+      <c r="D37" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="E37" s="156"/>
-      <c r="F37" s="156"/>
-      <c r="G37" s="156"/>
-      <c r="H37" s="156"/>
-      <c r="I37" s="156"/>
-      <c r="J37" s="156"/>
-      <c r="K37" s="156"/>
-      <c r="L37" s="156"/>
-      <c r="M37" s="156"/>
-      <c r="N37" s="156"/>
-      <c r="O37" s="156"/>
+      <c r="E37" s="169"/>
+      <c r="F37" s="169"/>
+      <c r="G37" s="169"/>
+      <c r="H37" s="169"/>
+      <c r="I37" s="169"/>
+      <c r="J37" s="169"/>
+      <c r="K37" s="169"/>
+      <c r="L37" s="169"/>
+      <c r="M37" s="169"/>
+      <c r="N37" s="169"/>
+      <c r="O37" s="169"/>
     </row>
     <row r="38" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D38" s="156"/>
-      <c r="E38" s="156"/>
-      <c r="F38" s="156"/>
-      <c r="G38" s="156"/>
-      <c r="H38" s="156"/>
-      <c r="I38" s="156"/>
-      <c r="J38" s="156"/>
-      <c r="K38" s="156"/>
-      <c r="L38" s="156"/>
-      <c r="M38" s="156"/>
-      <c r="N38" s="156"/>
-      <c r="O38" s="156"/>
+      <c r="D38" s="169"/>
+      <c r="E38" s="169"/>
+      <c r="F38" s="169"/>
+      <c r="G38" s="169"/>
+      <c r="H38" s="169"/>
+      <c r="I38" s="169"/>
+      <c r="J38" s="169"/>
+      <c r="K38" s="169"/>
+      <c r="L38" s="169"/>
+      <c r="M38" s="169"/>
+      <c r="N38" s="169"/>
+      <c r="O38" s="169"/>
     </row>
     <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D39" s="156"/>
-      <c r="E39" s="156"/>
-      <c r="F39" s="156"/>
-      <c r="G39" s="156"/>
-      <c r="H39" s="156"/>
-      <c r="I39" s="156"/>
-      <c r="J39" s="156"/>
-      <c r="K39" s="156"/>
-      <c r="L39" s="156"/>
-      <c r="M39" s="156"/>
-      <c r="N39" s="156"/>
-      <c r="O39" s="156"/>
+      <c r="D39" s="169"/>
+      <c r="E39" s="169"/>
+      <c r="F39" s="169"/>
+      <c r="G39" s="169"/>
+      <c r="H39" s="169"/>
+      <c r="I39" s="169"/>
+      <c r="J39" s="169"/>
+      <c r="K39" s="169"/>
+      <c r="L39" s="169"/>
+      <c r="M39" s="169"/>
+      <c r="N39" s="169"/>
+      <c r="O39" s="169"/>
     </row>
     <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D40" s="156"/>
-      <c r="E40" s="156"/>
-      <c r="F40" s="156"/>
-      <c r="G40" s="156"/>
-      <c r="H40" s="156"/>
-      <c r="I40" s="156"/>
-      <c r="J40" s="156"/>
-      <c r="K40" s="156"/>
-      <c r="L40" s="156"/>
-      <c r="M40" s="156"/>
-      <c r="N40" s="156"/>
-      <c r="O40" s="156"/>
+      <c r="D40" s="169"/>
+      <c r="E40" s="169"/>
+      <c r="F40" s="169"/>
+      <c r="G40" s="169"/>
+      <c r="H40" s="169"/>
+      <c r="I40" s="169"/>
+      <c r="J40" s="169"/>
+      <c r="K40" s="169"/>
+      <c r="L40" s="169"/>
+      <c r="M40" s="169"/>
+      <c r="N40" s="169"/>
+      <c r="O40" s="169"/>
     </row>
     <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D41" s="156"/>
-      <c r="E41" s="156"/>
-      <c r="F41" s="156"/>
-      <c r="G41" s="156"/>
-      <c r="H41" s="156"/>
-      <c r="I41" s="156"/>
-      <c r="J41" s="156"/>
-      <c r="K41" s="156"/>
-      <c r="L41" s="156"/>
-      <c r="M41" s="156"/>
-      <c r="N41" s="156"/>
-      <c r="O41" s="156"/>
+      <c r="D41" s="169"/>
+      <c r="E41" s="169"/>
+      <c r="F41" s="169"/>
+      <c r="G41" s="169"/>
+      <c r="H41" s="169"/>
+      <c r="I41" s="169"/>
+      <c r="J41" s="169"/>
+      <c r="K41" s="169"/>
+      <c r="L41" s="169"/>
+      <c r="M41" s="169"/>
+      <c r="N41" s="169"/>
+      <c r="O41" s="169"/>
     </row>
     <row r="42" spans="1:17" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D42" s="156"/>
-      <c r="E42" s="156"/>
-      <c r="F42" s="156"/>
-      <c r="G42" s="156"/>
-      <c r="H42" s="156"/>
-      <c r="I42" s="156"/>
-      <c r="J42" s="156"/>
-      <c r="K42" s="156"/>
-      <c r="L42" s="156"/>
-      <c r="M42" s="156"/>
-      <c r="N42" s="156"/>
-      <c r="O42" s="156"/>
+      <c r="D42" s="169"/>
+      <c r="E42" s="169"/>
+      <c r="F42" s="169"/>
+      <c r="G42" s="169"/>
+      <c r="H42" s="169"/>
+      <c r="I42" s="169"/>
+      <c r="J42" s="169"/>
+      <c r="K42" s="169"/>
+      <c r="L42" s="169"/>
+      <c r="M42" s="169"/>
+      <c r="N42" s="169"/>
+      <c r="O42" s="169"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="F4:F5"/>
     <mergeCell ref="B1:K3"/>
     <mergeCell ref="P4:P5"/>
     <mergeCell ref="D37:O42"/>
@@ -4839,13 +4865,23 @@
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="N4:N5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="F4:F5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B56D240-6D8B-4144-A545-69291A6FAA07}">
+  <dimension ref="C3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="3" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C3" s="201" t="s">
+        <v>188</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/2026/COLOMBRES/ENERO/Enero COLOMBRES 360.xlsx
+++ b/2026/COLOMBRES/ENERO/Enero COLOMBRES 360.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\2026\COLOMBRES\ENERO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\COLOMBRES\ENERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27712371-77F0-4A55-B386-3C097BB489AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70D4896D-81A6-4227-9BD8-211FAF0CFC32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="190">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -598,6 +598,9 @@
   </si>
   <si>
     <t>Los depositos sin identificar del 15/01 son de sergio</t>
+  </si>
+  <si>
+    <t>El 1B mando un mail desde soniases2020@icloud.com para que verifiquemos que no tiene deuda alguno, mando todos sus comprobantes desde hace mucho tiempo 226497,02 - Deben abonar    337.700,02</t>
   </si>
 </sst>
 </file>
@@ -800,7 +803,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -879,6 +882,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="30">
     <border>
@@ -1237,7 +1246,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="202">
+  <cellXfs count="213">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1463,117 +1472,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="20" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1586,6 +1484,132 @@
     <xf numFmtId="44" fontId="20" fillId="13" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="20" fillId="13" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="20" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="20" fillId="14" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="14" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="14" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="14" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="14" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1941,19 +1965,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L119"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="18.44140625" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="18.28515625" customWidth="1"/>
+    <col min="11" max="11" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="114" t="s">
         <v>122</v>
       </c>
@@ -1961,7 +1985,7 @@
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="109" t="s">
         <v>123</v>
       </c>
@@ -1969,7 +1993,7 @@
       <c r="C2" s="109"/>
       <c r="D2" s="109"/>
     </row>
-    <row r="3" spans="1:4" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="109" t="s">
         <v>152</v>
       </c>
@@ -1977,76 +2001,76 @@
       <c r="C3" s="109"/>
       <c r="D3" s="109"/>
     </row>
-    <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="160" t="s">
+    <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="181" t="s">
         <v>124</v>
       </c>
-      <c r="B4" s="160"/>
+      <c r="B4" s="181"/>
       <c r="C4" s="110"/>
       <c r="D4" s="110"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="160"/>
-      <c r="B5" s="160"/>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="181"/>
+      <c r="B5" s="181"/>
       <c r="C5" s="110"/>
       <c r="D5" s="110"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="160"/>
-      <c r="B6" s="160"/>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="181"/>
+      <c r="B6" s="181"/>
       <c r="C6" s="110"/>
       <c r="D6" s="110"/>
     </row>
-    <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="160"/>
-      <c r="B7" s="160"/>
+    <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="181"/>
+      <c r="B7" s="181"/>
       <c r="C7" s="110"/>
       <c r="D7" s="110"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="157" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B9" s="178" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="157"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="157"/>
-    </row>
-    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="161" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B10" s="178"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B11" s="178"/>
+    </row>
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="182" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="161"/>
-      <c r="C14" s="161"/>
-      <c r="D14" s="161"/>
-    </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="161"/>
-      <c r="B15" s="161"/>
-      <c r="C15" s="161"/>
-      <c r="D15" s="161"/>
-    </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="161"/>
-      <c r="B16" s="161"/>
-      <c r="C16" s="161"/>
-      <c r="D16" s="161"/>
-    </row>
-    <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="161"/>
-      <c r="B17" s="161"/>
-      <c r="C17" s="161"/>
-      <c r="D17" s="161"/>
-    </row>
-    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="182"/>
+      <c r="C14" s="182"/>
+      <c r="D14" s="182"/>
+    </row>
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="182"/>
+      <c r="B15" s="182"/>
+      <c r="C15" s="182"/>
+      <c r="D15" s="182"/>
+    </row>
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="182"/>
+      <c r="B16" s="182"/>
+      <c r="C16" s="182"/>
+      <c r="D16" s="182"/>
+    </row>
+    <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="182"/>
+      <c r="B17" s="182"/>
+      <c r="C17" s="182"/>
+      <c r="D17" s="182"/>
+    </row>
+    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>26</v>
       </c>
@@ -2054,7 +2078,7 @@
       <c r="C21" s="9"/>
       <c r="D21" s="13"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="26" t="s">
         <v>80</v>
       </c>
@@ -2062,7 +2086,7 @@
       <c r="C22" s="24"/>
       <c r="D22" s="24"/>
     </row>
-    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>130</v>
       </c>
@@ -2074,7 +2098,7 @@
       </c>
       <c r="D23" s="80"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>84</v>
       </c>
@@ -2085,7 +2109,7 @@
       </c>
       <c r="D24" s="80"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>83</v>
       </c>
@@ -2096,14 +2120,14 @@
       <c r="D25" s="80"/>
       <c r="G25" s="14"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="137"/>
       <c r="D26" s="80"/>
       <c r="G26" s="14"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="47" t="s">
         <v>82</v>
       </c>
@@ -2113,12 +2137,12 @@
         <v>1041158.0000000001</v>
       </c>
       <c r="D27" s="81"/>
-      <c r="F27" s="155" t="s">
+      <c r="F27" s="176" t="s">
         <v>145</v>
       </c>
-      <c r="G27" s="156"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G27" s="177"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>129</v>
       </c>
@@ -2130,7 +2154,7 @@
       </c>
       <c r="D28" s="113"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>81</v>
       </c>
@@ -2140,7 +2164,7 @@
       </c>
       <c r="D29" s="113"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>83</v>
       </c>
@@ -2150,13 +2174,13 @@
       </c>
       <c r="D30" s="113"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="138"/>
       <c r="D31" s="113"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="47" t="s">
         <v>82</v>
       </c>
@@ -2167,7 +2191,7 @@
       </c>
       <c r="D32" s="81"/>
     </row>
-    <row r="33" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="18" t="s">
         <v>0</v>
       </c>
@@ -2180,7 +2204,7 @@
       <c r="E33" s="14"/>
       <c r="F33" s="14"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="26" t="s">
         <v>38</v>
       </c>
@@ -2189,7 +2213,7 @@
       <c r="D34" s="83"/>
       <c r="F34" s="14"/>
     </row>
-    <row r="35" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="56" t="s">
         <v>39</v>
       </c>
@@ -2202,7 +2226,7 @@
       </c>
       <c r="G35" s="14"/>
     </row>
-    <row r="36" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="115" t="s">
         <v>131</v>
       </c>
@@ -2217,7 +2241,7 @@
       </c>
       <c r="G36" s="14"/>
     </row>
-    <row r="37" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="18" t="s">
         <v>34</v>
       </c>
@@ -2228,7 +2252,7 @@
         <v>281800</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="24" t="s">
         <v>77</v>
       </c>
@@ -2236,21 +2260,21 @@
       <c r="C38" s="28"/>
       <c r="D38" s="57"/>
     </row>
-    <row r="39" spans="1:7" s="33" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="158" t="s">
+    <row r="39" spans="1:7" s="33" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="179" t="s">
         <v>127</v>
       </c>
-      <c r="B39" s="159"/>
+      <c r="B39" s="180"/>
       <c r="C39" s="139" t="s">
         <v>180</v>
       </c>
       <c r="D39" s="123"/>
     </row>
-    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="158" t="s">
+    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="179" t="s">
         <v>128</v>
       </c>
-      <c r="B40" s="159"/>
+      <c r="B40" s="180"/>
       <c r="C40" s="146">
         <v>4203</v>
       </c>
@@ -2258,7 +2282,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="25" t="s">
         <v>1</v>
       </c>
@@ -2269,7 +2293,7 @@
         <v>4203</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="24" t="s">
         <v>35</v>
       </c>
@@ -2277,7 +2301,7 @@
       <c r="C42" s="31"/>
       <c r="D42" s="85"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="80" t="s">
         <v>132</v>
       </c>
@@ -2292,7 +2316,7 @@
       </c>
       <c r="F43" s="116"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="80" t="s">
         <v>133</v>
       </c>
@@ -2306,7 +2330,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="80" t="s">
         <v>134</v>
       </c>
@@ -2321,7 +2345,7 @@
         <v>Debito 13/01</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="80" t="s">
         <v>135</v>
       </c>
@@ -2336,7 +2360,7 @@
         <v>Debito 13/01</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="25" t="s">
         <v>2</v>
       </c>
@@ -2347,7 +2371,7 @@
         <v>2721617.26</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="24" t="s">
         <v>37</v>
       </c>
@@ -2355,7 +2379,7 @@
       <c r="C48" s="31"/>
       <c r="D48" s="85"/>
     </row>
-    <row r="49" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="95" t="s">
         <v>136</v>
       </c>
@@ -2367,7 +2391,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="80" t="s">
         <v>125</v>
       </c>
@@ -2382,7 +2406,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="80" t="s">
         <v>138</v>
       </c>
@@ -2394,11 +2418,11 @@
         <v>167</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="167" t="s">
+    <row r="52" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="188" t="s">
         <v>157</v>
       </c>
-      <c r="B52" s="168"/>
+      <c r="B52" s="189"/>
       <c r="C52" s="148">
         <v>204149</v>
       </c>
@@ -2406,11 +2430,11 @@
         <v>175</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="165" t="s">
+    <row r="53" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="186" t="s">
         <v>170</v>
       </c>
-      <c r="B53" s="166"/>
+      <c r="B53" s="187"/>
       <c r="C53" s="148">
         <v>100000</v>
       </c>
@@ -2418,11 +2442,11 @@
         <v>171</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="158" t="s">
+    <row r="54" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="179" t="s">
         <v>153</v>
       </c>
-      <c r="B54" s="159"/>
+      <c r="B54" s="180"/>
       <c r="C54" s="148">
         <v>35200</v>
       </c>
@@ -2430,7 +2454,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="25" t="s">
         <v>3</v>
       </c>
@@ -2441,7 +2465,7 @@
         <v>1793121.85</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="24" t="s">
         <v>36</v>
       </c>
@@ -2449,7 +2473,7 @@
       <c r="C56" s="30"/>
       <c r="D56" s="87"/>
     </row>
-    <row r="57" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="149" t="s">
         <v>164</v>
       </c>
@@ -2461,7 +2485,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="149" t="s">
         <v>182</v>
       </c>
@@ -2473,7 +2497,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="151" t="s">
         <v>165</v>
       </c>
@@ -2485,11 +2509,11 @@
         <v>166</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="158" t="s">
+    <row r="60" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="179" t="s">
         <v>177</v>
       </c>
-      <c r="B60" s="159"/>
+      <c r="B60" s="180"/>
       <c r="C60" s="148">
         <v>250000</v>
       </c>
@@ -2497,7 +2521,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="151" t="s">
         <v>173</v>
       </c>
@@ -2509,11 +2533,11 @@
         <v>174</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="158" t="s">
+    <row r="62" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="179" t="s">
         <v>168</v>
       </c>
-      <c r="B62" s="159"/>
+      <c r="B62" s="180"/>
       <c r="C62" s="148">
         <v>750000</v>
       </c>
@@ -2521,7 +2545,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="144" t="s">
         <v>184</v>
       </c>
@@ -2533,11 +2557,11 @@
         <v>185</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="158" t="s">
+    <row r="64" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="179" t="s">
         <v>183</v>
       </c>
-      <c r="B64" s="159"/>
+      <c r="B64" s="180"/>
       <c r="C64" s="148">
         <v>180000</v>
       </c>
@@ -2545,11 +2569,11 @@
         <v>178</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="158" t="s">
+    <row r="65" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="179" t="s">
         <v>161</v>
       </c>
-      <c r="B65" s="159"/>
+      <c r="B65" s="180"/>
       <c r="C65" s="148">
         <v>35000</v>
       </c>
@@ -2559,17 +2583,17 @@
       <c r="E65" s="39"/>
       <c r="F65" s="39"/>
     </row>
-    <row r="66" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="165" t="s">
+    <row r="66" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="186" t="s">
         <v>158</v>
       </c>
-      <c r="B66" s="166"/>
+      <c r="B66" s="187"/>
       <c r="C66" s="140">
         <v>0</v>
       </c>
       <c r="D66" s="122"/>
     </row>
-    <row r="67" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="25" t="s">
         <v>11</v>
       </c>
@@ -2580,7 +2604,7 @@
         <v>1641387.8800000001</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="24" t="s">
         <v>29</v>
       </c>
@@ -2588,7 +2612,7 @@
       <c r="C68" s="19"/>
       <c r="D68" s="87"/>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="80" t="s">
         <v>137</v>
       </c>
@@ -2598,7 +2622,7 @@
       </c>
       <c r="D69" s="91"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="80" t="s">
         <v>126</v>
       </c>
@@ -2609,7 +2633,7 @@
       </c>
       <c r="D70" s="89"/>
     </row>
-    <row r="71" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="44" t="s">
         <v>34</v>
       </c>
@@ -2620,30 +2644,30 @@
         <v>202097.86</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="5"/>
       <c r="B72" s="5"/>
       <c r="C72" s="80"/>
       <c r="D72" s="93"/>
     </row>
-    <row r="73" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="162" t="s">
+    <row r="73" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="183" t="s">
         <v>144</v>
       </c>
-      <c r="B73" s="163"/>
-      <c r="C73" s="164"/>
+      <c r="B73" s="184"/>
+      <c r="C73" s="185"/>
       <c r="D73" s="94">
         <f>10000000-8703429.85</f>
         <v>1296570.1500000004</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="1"/>
       <c r="C74" s="95"/>
       <c r="D74" s="96"/>
       <c r="E74" s="39"/>
     </row>
-    <row r="75" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="3" t="s">
         <v>30</v>
       </c>
@@ -2656,16 +2680,16 @@
       <c r="E75" s="39"/>
       <c r="F75" s="39"/>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C76" s="95"/>
       <c r="D76" s="95"/>
       <c r="F76" s="117"/>
     </row>
-    <row r="77" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C77" s="95"/>
       <c r="D77" s="95"/>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="11" t="s">
         <v>40</v>
       </c>
@@ -2673,25 +2697,25 @@
       <c r="C78" s="99"/>
       <c r="D78" s="100"/>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="172"/>
-      <c r="B79" s="173"/>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79" s="193"/>
+      <c r="B79" s="194"/>
       <c r="C79" s="88"/>
       <c r="D79" s="86"/>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="172"/>
-      <c r="B80" s="173"/>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A80" s="193"/>
+      <c r="B80" s="194"/>
       <c r="C80" s="88"/>
       <c r="D80" s="86"/>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="103"/>
       <c r="B81" s="104"/>
       <c r="C81" s="88"/>
       <c r="D81" s="86"/>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="42"/>
       <c r="B82" s="41"/>
       <c r="C82" s="49"/>
@@ -2700,9 +2724,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="84" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="20" t="s">
         <v>41</v>
       </c>
@@ -2712,8 +2736,8 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="87" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="87" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="3" t="s">
         <v>42</v>
       </c>
@@ -2724,8 +2748,8 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="89" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="89" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="78" t="s">
         <v>31</v>
       </c>
@@ -2735,7 +2759,7 @@
       </c>
       <c r="C89" s="39"/>
     </row>
-    <row r="90" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="78" t="s">
         <v>32</v>
       </c>
@@ -2744,7 +2768,7 @@
         <v>8703429.8499999996</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="78" t="s">
         <v>43</v>
       </c>
@@ -2753,7 +2777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="78" t="s">
         <v>88</v>
       </c>
@@ -2762,33 +2786,33 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" s="171" t="s">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A95" s="192" t="s">
         <v>159</v>
       </c>
-      <c r="B95" s="171"/>
-      <c r="C95" s="171"/>
-      <c r="D95" s="171"/>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A96" s="171"/>
-      <c r="B96" s="171"/>
-      <c r="C96" s="171"/>
-      <c r="D96" s="171"/>
-    </row>
-    <row r="97" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="171"/>
-      <c r="B97" s="171"/>
-      <c r="C97" s="171"/>
-      <c r="D97" s="171"/>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B95" s="192"/>
+      <c r="C95" s="192"/>
+      <c r="D95" s="192"/>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A96" s="192"/>
+      <c r="B96" s="192"/>
+      <c r="C96" s="192"/>
+      <c r="D96" s="192"/>
+    </row>
+    <row r="97" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="192"/>
+      <c r="B97" s="192"/>
+      <c r="C97" s="192"/>
+      <c r="D97" s="192"/>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="15" t="s">
         <v>79</v>
       </c>
       <c r="B99" s="35"/>
     </row>
-    <row r="100" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="23" t="s">
         <v>33</v>
       </c>
@@ -2796,16 +2820,16 @@
         <v>5322816.5199999996</v>
       </c>
     </row>
-    <row r="101" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="16" t="s">
         <v>91</v>
       </c>
       <c r="B101" s="36">
         <f>PRORRATEO!H34</f>
-        <v>9786183.0700000003</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10051349.09</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="16" t="s">
         <v>90</v>
       </c>
@@ -2814,13 +2838,13 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="17" t="s">
         <v>143</v>
       </c>
       <c r="B103" s="119"/>
     </row>
-    <row r="104" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="17" t="s">
         <v>176</v>
       </c>
@@ -2828,7 +2852,7 @@
         <v>-31400</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="34" t="s">
         <v>44</v>
       </c>
@@ -2837,7 +2861,7 @@
         <v>-8703429.8499999996</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="17" t="s">
         <v>45</v>
       </c>
@@ -2846,30 +2870,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="22" t="s">
         <v>11</v>
       </c>
       <c r="B107" s="105">
         <f>SUM(B100:B106)</f>
-        <v>6874169.7400000002</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>7139335.7599999998</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B108" s="37"/>
       <c r="C108" s="39"/>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A110" s="170" t="s">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A110" s="191" t="s">
         <v>78</v>
       </c>
-      <c r="B110" s="170"/>
-    </row>
-    <row r="111" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="170"/>
-      <c r="B111" s="170"/>
-    </row>
-    <row r="112" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B110" s="191"/>
+    </row>
+    <row r="111" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="191"/>
+      <c r="B111" s="191"/>
+    </row>
+    <row r="112" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="101" t="s">
         <v>186</v>
       </c>
@@ -2877,7 +2901,7 @@
         <v>240000</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="101" t="s">
         <v>186</v>
       </c>
@@ -2885,7 +2909,7 @@
         <v>260000</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" s="40" t="s">
         <v>11</v>
       </c>
@@ -2894,32 +2918,32 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L115" s="8"/>
     </row>
-    <row r="116" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="169"/>
-      <c r="B116" s="169"/>
-      <c r="C116" s="169"/>
-      <c r="D116" s="169"/>
-    </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A117" s="169"/>
-      <c r="B117" s="169"/>
-      <c r="C117" s="169"/>
-      <c r="D117" s="169"/>
-    </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A118" s="169"/>
-      <c r="B118" s="169"/>
-      <c r="C118" s="169"/>
-      <c r="D118" s="169"/>
-    </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A119" s="169"/>
-      <c r="B119" s="169"/>
-      <c r="C119" s="169"/>
-      <c r="D119" s="169"/>
+    <row r="116" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="190"/>
+      <c r="B116" s="190"/>
+      <c r="C116" s="190"/>
+      <c r="D116" s="190"/>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A117" s="190"/>
+      <c r="B117" s="190"/>
+      <c r="C117" s="190"/>
+      <c r="D117" s="190"/>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A118" s="190"/>
+      <c r="B118" s="190"/>
+      <c r="C118" s="190"/>
+      <c r="D118" s="190"/>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A119" s="190"/>
+      <c r="B119" s="190"/>
+      <c r="C119" s="190"/>
+      <c r="D119" s="190"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -2953,61 +2977,61 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:S42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5703125" customWidth="1"/>
-    <col min="3" max="3" width="4.28515625" customWidth="1"/>
-    <col min="4" max="4" width="18.5703125" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="5.140625" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" customWidth="1"/>
+    <col min="2" max="2" width="5.5546875" customWidth="1"/>
+    <col min="3" max="3" width="4.33203125" customWidth="1"/>
+    <col min="4" max="4" width="18.5546875" customWidth="1"/>
+    <col min="5" max="5" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="5.109375" customWidth="1"/>
+    <col min="7" max="7" width="14.109375" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="7.7109375" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5703125" customWidth="1"/>
-    <col min="11" max="11" width="11.140625" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" customWidth="1"/>
-    <col min="13" max="13" width="12.42578125" customWidth="1"/>
-    <col min="14" max="14" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.28515625" customWidth="1"/>
-    <col min="16" max="16" width="14.140625" customWidth="1"/>
-    <col min="17" max="17" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.6640625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5546875" customWidth="1"/>
+    <col min="11" max="11" width="11.109375" customWidth="1"/>
+    <col min="12" max="12" width="14.44140625" customWidth="1"/>
+    <col min="13" max="13" width="12.44140625" customWidth="1"/>
+    <col min="14" max="14" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.33203125" customWidth="1"/>
+    <col min="16" max="16" width="14.109375" customWidth="1"/>
+    <col min="17" max="17" width="7.44140625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
-      <c r="B1" s="174" t="s">
+      <c r="B1" s="195" t="s">
         <v>147</v>
       </c>
-      <c r="C1" s="174"/>
-      <c r="D1" s="174"/>
-      <c r="E1" s="174"/>
-      <c r="F1" s="174"/>
-      <c r="G1" s="174"/>
-      <c r="H1" s="174"/>
-      <c r="I1" s="174"/>
-      <c r="J1" s="174"/>
-      <c r="K1" s="174"/>
+      <c r="C1" s="195"/>
+      <c r="D1" s="195"/>
+      <c r="E1" s="195"/>
+      <c r="F1" s="195"/>
+      <c r="G1" s="195"/>
+      <c r="H1" s="195"/>
+      <c r="I1" s="195"/>
+      <c r="J1" s="195"/>
+      <c r="K1" s="195"/>
       <c r="L1" s="6"/>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
       <c r="O1" s="6"/>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
-      <c r="B2" s="174"/>
-      <c r="C2" s="174"/>
-      <c r="D2" s="174"/>
-      <c r="E2" s="174"/>
-      <c r="F2" s="174"/>
-      <c r="G2" s="174"/>
-      <c r="H2" s="174"/>
-      <c r="I2" s="174"/>
-      <c r="J2" s="174"/>
-      <c r="K2" s="174"/>
+      <c r="B2" s="195"/>
+      <c r="C2" s="195"/>
+      <c r="D2" s="195"/>
+      <c r="E2" s="195"/>
+      <c r="F2" s="195"/>
+      <c r="G2" s="195"/>
+      <c r="H2" s="195"/>
+      <c r="I2" s="195"/>
+      <c r="J2" s="195"/>
+      <c r="K2" s="195"/>
       <c r="L2" s="7" t="s">
         <v>4</v>
       </c>
@@ -3019,18 +3043,18 @@
       <c r="P2" s="46"/>
       <c r="Q2" s="14"/>
     </row>
-    <row r="3" spans="1:19" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
-      <c r="B3" s="175"/>
-      <c r="C3" s="175"/>
-      <c r="D3" s="175"/>
-      <c r="E3" s="175"/>
-      <c r="F3" s="175"/>
-      <c r="G3" s="175"/>
-      <c r="H3" s="175"/>
-      <c r="I3" s="175"/>
-      <c r="J3" s="175"/>
-      <c r="K3" s="175"/>
+      <c r="B3" s="196"/>
+      <c r="C3" s="196"/>
+      <c r="D3" s="196"/>
+      <c r="E3" s="196"/>
+      <c r="F3" s="196"/>
+      <c r="G3" s="196"/>
+      <c r="H3" s="196"/>
+      <c r="I3" s="196"/>
+      <c r="J3" s="196"/>
+      <c r="K3" s="196"/>
       <c r="L3" s="7" t="s">
         <v>93</v>
       </c>
@@ -3041,79 +3065,79 @@
       </c>
       <c r="P3" s="50"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="188" t="s">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A4" s="209" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="190" t="s">
+      <c r="B4" s="211" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="178" t="s">
+      <c r="C4" s="199" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="178" t="s">
+      <c r="D4" s="199" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="178" t="s">
+      <c r="E4" s="199" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="178" t="s">
+      <c r="F4" s="199" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="178" t="s">
+      <c r="G4" s="199" t="s">
         <v>89</v>
       </c>
-      <c r="H4" s="178" t="s">
+      <c r="H4" s="199" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="178" t="s">
+      <c r="I4" s="199" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="183" t="s">
+      <c r="J4" s="204" t="s">
         <v>50</v>
       </c>
-      <c r="K4" s="180" t="s">
+      <c r="K4" s="201" t="s">
         <v>47</v>
       </c>
-      <c r="L4" s="180" t="s">
+      <c r="L4" s="201" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="180" t="s">
+      <c r="M4" s="201" t="s">
         <v>46</v>
       </c>
-      <c r="N4" s="186" t="s">
+      <c r="N4" s="207" t="s">
         <v>87</v>
       </c>
       <c r="O4" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="P4" s="176" t="s">
+      <c r="P4" s="197" t="s">
         <v>85</v>
       </c>
       <c r="S4" s="39"/>
     </row>
-    <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="189"/>
-      <c r="B5" s="191"/>
-      <c r="C5" s="182"/>
-      <c r="D5" s="182"/>
-      <c r="E5" s="179"/>
-      <c r="F5" s="182"/>
-      <c r="G5" s="182"/>
-      <c r="H5" s="182"/>
-      <c r="I5" s="179"/>
-      <c r="J5" s="184"/>
-      <c r="K5" s="181"/>
-      <c r="L5" s="185"/>
-      <c r="M5" s="181"/>
-      <c r="N5" s="187"/>
+    <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="210"/>
+      <c r="B5" s="212"/>
+      <c r="C5" s="203"/>
+      <c r="D5" s="203"/>
+      <c r="E5" s="200"/>
+      <c r="F5" s="203"/>
+      <c r="G5" s="203"/>
+      <c r="H5" s="203"/>
+      <c r="I5" s="200"/>
+      <c r="J5" s="205"/>
+      <c r="K5" s="202"/>
+      <c r="L5" s="206"/>
+      <c r="M5" s="202"/>
+      <c r="N5" s="208"/>
       <c r="O5" s="51" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 16/02</v>
       </c>
-      <c r="P5" s="177"/>
-    </row>
-    <row r="6" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P5" s="198"/>
+    </row>
+    <row r="6" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>12</v>
       </c>
@@ -3169,57 +3193,57 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="54">
+      <c r="B7" s="165">
         <v>2</v>
       </c>
-      <c r="C7" s="54" t="s">
+      <c r="C7" s="165" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="54" t="s">
+      <c r="D7" s="165" t="s">
         <v>96</v>
       </c>
-      <c r="E7" s="55"/>
-      <c r="F7" s="59">
+      <c r="E7" s="166"/>
+      <c r="F7" s="167">
         <v>3.07</v>
       </c>
-      <c r="G7" s="60">
+      <c r="G7" s="168">
         <v>909166.02</v>
       </c>
-      <c r="H7" s="61">
-        <f>177000+307000+160000</f>
-        <v>644000</v>
-      </c>
-      <c r="I7" s="62"/>
-      <c r="J7" s="63">
+      <c r="H7" s="168">
+        <f>177000+307000+160000+226497.02+38669</f>
+        <v>909166.02</v>
+      </c>
+      <c r="I7" s="169"/>
+      <c r="J7" s="170">
         <f t="shared" ref="J7:J31" si="2">G7-H7</f>
-        <v>265166.02</v>
-      </c>
-      <c r="K7" s="63">
+        <v>0</v>
+      </c>
+      <c r="K7" s="170">
         <f t="shared" ref="K7:K32" si="3">IF(J7&gt;0,J7*2.95%,0)</f>
-        <v>7822.3975900000014</v>
-      </c>
-      <c r="L7" s="64">
+        <v>0</v>
+      </c>
+      <c r="L7" s="171">
         <f t="shared" ref="L7:L33" si="4">O$3*F7%</f>
         <v>30699.999999999996</v>
       </c>
-      <c r="M7" s="64">
+      <c r="M7" s="171">
         <f t="shared" ref="M7:M33" si="5">O$2*F7%</f>
         <v>307000</v>
       </c>
-      <c r="N7" s="65">
-        <v>0</v>
-      </c>
-      <c r="O7" s="66">
+      <c r="N7" s="172">
+        <v>0</v>
+      </c>
+      <c r="O7" s="173">
         <f t="shared" si="0"/>
-        <v>610688.02</v>
-      </c>
-      <c r="P7" s="67">
+        <v>337700.02</v>
+      </c>
+      <c r="P7" s="174">
         <f t="shared" si="1"/>
-        <v>629009.02</v>
+        <v>347831.02</v>
       </c>
       <c r="Q7" s="39">
         <f>Q6+0.01</f>
@@ -3229,7 +3253,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>13</v>
       </c>
@@ -3283,7 +3307,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>14</v>
       </c>
@@ -3343,7 +3367,7 @@
       </c>
       <c r="S9" s="39"/>
     </row>
-    <row r="10" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>14</v>
       </c>
@@ -3401,7 +3425,7 @@
       </c>
       <c r="S10" s="39"/>
     </row>
-    <row r="11" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>15</v>
       </c>
@@ -3458,52 +3482,52 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="192">
+      <c r="B12" s="155">
         <v>7</v>
       </c>
-      <c r="C12" s="192" t="s">
+      <c r="C12" s="155" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="192" t="s">
+      <c r="D12" s="155" t="s">
         <v>100</v>
       </c>
-      <c r="E12" s="192"/>
-      <c r="F12" s="193">
+      <c r="E12" s="155"/>
+      <c r="F12" s="156">
         <v>4.55</v>
       </c>
-      <c r="G12" s="194">
+      <c r="G12" s="157">
         <v>496500.07</v>
       </c>
-      <c r="H12" s="194"/>
-      <c r="I12" s="195"/>
-      <c r="J12" s="196">
+      <c r="H12" s="157"/>
+      <c r="I12" s="158"/>
+      <c r="J12" s="159">
         <f t="shared" si="2"/>
         <v>496500.07</v>
       </c>
-      <c r="K12" s="196">
+      <c r="K12" s="159">
         <f t="shared" si="3"/>
         <v>14646.752065000001</v>
       </c>
-      <c r="L12" s="197">
+      <c r="L12" s="160">
         <f t="shared" si="4"/>
         <v>45500</v>
       </c>
-      <c r="M12" s="197">
+      <c r="M12" s="160">
         <f t="shared" si="5"/>
         <v>455000</v>
       </c>
-      <c r="N12" s="198">
-        <v>0</v>
-      </c>
-      <c r="O12" s="199">
+      <c r="N12" s="161">
+        <v>0</v>
+      </c>
+      <c r="O12" s="162">
         <f t="shared" si="0"/>
         <v>1011647.07</v>
       </c>
-      <c r="P12" s="200">
+      <c r="P12" s="163">
         <f t="shared" si="1"/>
         <v>1041996.07</v>
       </c>
@@ -3514,7 +3538,7 @@
       <c r="R12" s="117"/>
       <c r="S12" s="116"/>
     </row>
-    <row r="13" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>16</v>
       </c>
@@ -3570,7 +3594,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -3629,7 +3653,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>17</v>
       </c>
@@ -3689,7 +3713,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>17</v>
       </c>
@@ -3745,7 +3769,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>18</v>
       </c>
@@ -3801,7 +3825,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>18</v>
       </c>
@@ -3858,7 +3882,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>19</v>
       </c>
@@ -3915,7 +3939,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>19</v>
       </c>
@@ -3972,7 +3996,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>20</v>
       </c>
@@ -4032,7 +4056,7 @@
       </c>
       <c r="S21" s="38"/>
     </row>
-    <row r="22" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>20</v>
       </c>
@@ -4086,7 +4110,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>21</v>
       </c>
@@ -4143,7 +4167,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>21</v>
       </c>
@@ -4200,7 +4224,7 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>22</v>
       </c>
@@ -4260,7 +4284,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>23</v>
       </c>
@@ -4317,7 +4341,7 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>24</v>
       </c>
@@ -4374,7 +4398,7 @@
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>25</v>
       </c>
@@ -4431,7 +4455,7 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>27</v>
       </c>
@@ -4488,7 +4512,7 @@
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>27</v>
       </c>
@@ -4547,7 +4571,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>27</v>
       </c>
@@ -4608,7 +4632,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
         <v>27</v>
       </c>
@@ -4665,7 +4689,7 @@
         <v>0.27000000000000007</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
         <v>27</v>
       </c>
@@ -4711,7 +4735,7 @@
       </c>
       <c r="Q33" s="39"/>
     </row>
-    <row r="34" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B34" s="73"/>
       <c r="C34" s="74"/>
       <c r="D34" s="75"/>
@@ -4726,7 +4750,7 @@
       </c>
       <c r="H34" s="52">
         <f>SUM(H6:H33)</f>
-        <v>9786183.0700000003</v>
+        <v>10051349.09</v>
       </c>
       <c r="I34" s="52">
         <f t="shared" ref="I34" si="10">SUM(I6:I33)</f>
@@ -4748,103 +4772,103 @@
       </c>
       <c r="O34" s="77">
         <f>SUM(O6:O32)</f>
-        <v>12705899.779999999</v>
+        <v>12432911.779999999</v>
       </c>
       <c r="P34" s="77">
         <f>SUM(P6:P32)</f>
-        <v>13087077.779999999</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>12805899.780000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D35" s="43"/>
       <c r="E35" s="43"/>
     </row>
-    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D37" s="169" t="s">
+    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="37" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D37" s="190" t="s">
         <v>148</v>
       </c>
-      <c r="E37" s="169"/>
-      <c r="F37" s="169"/>
-      <c r="G37" s="169"/>
-      <c r="H37" s="169"/>
-      <c r="I37" s="169"/>
-      <c r="J37" s="169"/>
-      <c r="K37" s="169"/>
-      <c r="L37" s="169"/>
-      <c r="M37" s="169"/>
-      <c r="N37" s="169"/>
-      <c r="O37" s="169"/>
-    </row>
-    <row r="38" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D38" s="169"/>
-      <c r="E38" s="169"/>
-      <c r="F38" s="169"/>
-      <c r="G38" s="169"/>
-      <c r="H38" s="169"/>
-      <c r="I38" s="169"/>
-      <c r="J38" s="169"/>
-      <c r="K38" s="169"/>
-      <c r="L38" s="169"/>
-      <c r="M38" s="169"/>
-      <c r="N38" s="169"/>
-      <c r="O38" s="169"/>
-    </row>
-    <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D39" s="169"/>
-      <c r="E39" s="169"/>
-      <c r="F39" s="169"/>
-      <c r="G39" s="169"/>
-      <c r="H39" s="169"/>
-      <c r="I39" s="169"/>
-      <c r="J39" s="169"/>
-      <c r="K39" s="169"/>
-      <c r="L39" s="169"/>
-      <c r="M39" s="169"/>
-      <c r="N39" s="169"/>
-      <c r="O39" s="169"/>
-    </row>
-    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D40" s="169"/>
-      <c r="E40" s="169"/>
-      <c r="F40" s="169"/>
-      <c r="G40" s="169"/>
-      <c r="H40" s="169"/>
-      <c r="I40" s="169"/>
-      <c r="J40" s="169"/>
-      <c r="K40" s="169"/>
-      <c r="L40" s="169"/>
-      <c r="M40" s="169"/>
-      <c r="N40" s="169"/>
-      <c r="O40" s="169"/>
-    </row>
-    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D41" s="169"/>
-      <c r="E41" s="169"/>
-      <c r="F41" s="169"/>
-      <c r="G41" s="169"/>
-      <c r="H41" s="169"/>
-      <c r="I41" s="169"/>
-      <c r="J41" s="169"/>
-      <c r="K41" s="169"/>
-      <c r="L41" s="169"/>
-      <c r="M41" s="169"/>
-      <c r="N41" s="169"/>
-      <c r="O41" s="169"/>
-    </row>
-    <row r="42" spans="1:17" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D42" s="169"/>
-      <c r="E42" s="169"/>
-      <c r="F42" s="169"/>
-      <c r="G42" s="169"/>
-      <c r="H42" s="169"/>
-      <c r="I42" s="169"/>
-      <c r="J42" s="169"/>
-      <c r="K42" s="169"/>
-      <c r="L42" s="169"/>
-      <c r="M42" s="169"/>
-      <c r="N42" s="169"/>
-      <c r="O42" s="169"/>
+      <c r="E37" s="190"/>
+      <c r="F37" s="190"/>
+      <c r="G37" s="190"/>
+      <c r="H37" s="190"/>
+      <c r="I37" s="190"/>
+      <c r="J37" s="190"/>
+      <c r="K37" s="190"/>
+      <c r="L37" s="190"/>
+      <c r="M37" s="190"/>
+      <c r="N37" s="190"/>
+      <c r="O37" s="190"/>
+    </row>
+    <row r="38" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D38" s="190"/>
+      <c r="E38" s="190"/>
+      <c r="F38" s="190"/>
+      <c r="G38" s="190"/>
+      <c r="H38" s="190"/>
+      <c r="I38" s="190"/>
+      <c r="J38" s="190"/>
+      <c r="K38" s="190"/>
+      <c r="L38" s="190"/>
+      <c r="M38" s="190"/>
+      <c r="N38" s="190"/>
+      <c r="O38" s="190"/>
+    </row>
+    <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D39" s="190"/>
+      <c r="E39" s="190"/>
+      <c r="F39" s="190"/>
+      <c r="G39" s="190"/>
+      <c r="H39" s="190"/>
+      <c r="I39" s="190"/>
+      <c r="J39" s="190"/>
+      <c r="K39" s="190"/>
+      <c r="L39" s="190"/>
+      <c r="M39" s="190"/>
+      <c r="N39" s="190"/>
+      <c r="O39" s="190"/>
+    </row>
+    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D40" s="190"/>
+      <c r="E40" s="190"/>
+      <c r="F40" s="190"/>
+      <c r="G40" s="190"/>
+      <c r="H40" s="190"/>
+      <c r="I40" s="190"/>
+      <c r="J40" s="190"/>
+      <c r="K40" s="190"/>
+      <c r="L40" s="190"/>
+      <c r="M40" s="190"/>
+      <c r="N40" s="190"/>
+      <c r="O40" s="190"/>
+    </row>
+    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D41" s="190"/>
+      <c r="E41" s="190"/>
+      <c r="F41" s="190"/>
+      <c r="G41" s="190"/>
+      <c r="H41" s="190"/>
+      <c r="I41" s="190"/>
+      <c r="J41" s="190"/>
+      <c r="K41" s="190"/>
+      <c r="L41" s="190"/>
+      <c r="M41" s="190"/>
+      <c r="N41" s="190"/>
+      <c r="O41" s="190"/>
+    </row>
+    <row r="42" spans="1:17" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D42" s="190"/>
+      <c r="E42" s="190"/>
+      <c r="F42" s="190"/>
+      <c r="G42" s="190"/>
+      <c r="H42" s="190"/>
+      <c r="I42" s="190"/>
+      <c r="J42" s="190"/>
+      <c r="K42" s="190"/>
+      <c r="L42" s="190"/>
+      <c r="M42" s="190"/>
+      <c r="N42" s="190"/>
+      <c r="O42" s="190"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -4873,12 +4897,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B56D240-6D8B-4144-A545-69291A6FAA07}">
-  <dimension ref="C3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="C3:C6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="3" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C3" s="201" t="s">
+    <row r="3" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C3" s="164" t="s">
         <v>188</v>
+      </c>
+    </row>
+    <row r="6" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C6" s="175" t="s">
+        <v>189</v>
       </c>
     </row>
   </sheetData>
